--- a/base/pacotes/thozen-electra/executivo-thozen-electra.xlsx
+++ b/base/pacotes/thozen-electra/executivo-thozen-electra.xlsx
@@ -231,6 +231,9 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -241,9 +244,6 @@
     </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em 2026-04-13T17:12:02 | AC=37894 m² | UR=348 | baseado em 5 projetos similares</t>
+          <t>Gerado em 2026-04-13T22:57:58 | AC=37894 m² | UR=348 | baseado em 5 projetos similares</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
         <v>0.06817230780285365</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>0.005925894967140575</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>0.05661030412666304</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>0.01770443958642661</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>0.01405825355510858</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>0.02172377400794012</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>0.1188581925324598</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>0.05002323940878754</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>0.01402158060974169</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1482,100 +1482,12 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="24" t="inlineStr">
-        <is>
-          <t>Equipamentos de Climatização</t>
-        </is>
-      </c>
-      <c r="C5" s="23" t="inlineStr">
-        <is>
-          <t>vb</t>
-        </is>
-      </c>
-      <c r="D5" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="26" t="n">
-        <v>765314.6800000001</v>
-      </c>
-      <c r="F5" s="27" t="n">
-        <v>765314.6800000001</v>
-      </c>
-      <c r="G5" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="24" t="inlineStr">
-        <is>
-          <t>fg-scenarium</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="24" t="inlineStr">
-        <is>
-          <t>Mão de obra para instalações de climatização e exaustão</t>
-        </is>
-      </c>
-      <c r="C6" s="23" t="inlineStr">
-        <is>
-          <t>vb</t>
-        </is>
-      </c>
-      <c r="D6" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="26" t="n">
-        <v>387520</v>
-      </c>
-      <c r="F6" s="27" t="n">
-        <v>387520</v>
-      </c>
-      <c r="G6" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" s="24" t="inlineStr">
-        <is>
-          <t>fg-scenarium</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="24" t="inlineStr">
-        <is>
-          <t>Projeto De Climatização/Exautão</t>
-        </is>
-      </c>
-      <c r="C7" s="23" t="inlineStr">
-        <is>
-          <t>vb</t>
-        </is>
-      </c>
-      <c r="D7" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="26" t="n">
-        <v>52672.53</v>
-      </c>
-      <c r="F7" s="27" t="n">
-        <v>52672.53</v>
-      </c>
-      <c r="G7" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="24" t="inlineStr">
-        <is>
-          <t>fg-scenarium</t>
-        </is>
-      </c>
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>(sem detalhamento granular nos similares — usar valor agregado acima)</t>
+        </is>
+      </c>
+      <c r="B5" s="28" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1838,7 +1750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2041,59 +1953,27 @@
       </c>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>Projeto De Forro</t>
+          <t>Forro de madeira - material e mão de obra</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="D9" s="25" t="n">
-        <v>1</v>
+        <v>4.41</v>
       </c>
       <c r="E9" s="26" t="n">
-        <v>19025</v>
+        <v>579</v>
       </c>
       <c r="F9" s="27" t="n">
-        <v>19025</v>
+        <v>2553.39</v>
       </c>
       <c r="G9" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H9" s="24" t="inlineStr">
-        <is>
-          <t>fg-scenarium</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="23" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="24" t="inlineStr">
-        <is>
-          <t>Forro de madeira - material e mão de obra</t>
-        </is>
-      </c>
-      <c r="C10" s="23" t="inlineStr">
-        <is>
-          <t>m2</t>
-        </is>
-      </c>
-      <c r="D10" s="25" t="n">
-        <v>4.41</v>
-      </c>
-      <c r="E10" s="26" t="n">
-        <v>579</v>
-      </c>
-      <c r="F10" s="27" t="n">
-        <v>2553.39</v>
-      </c>
-      <c r="G10" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="24" t="inlineStr">
         <is>
           <t>fg-scenarium</t>
         </is>
@@ -3693,7 +3573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -4024,22 +3904,22 @@
       </c>
       <c r="B13" s="24" t="inlineStr">
         <is>
-          <t>Consultorias Técnicas De Esquadrias</t>
+          <t>Porta de madeira- correr (trilho lateral) - folha leve/média - 70x210cm (kit completo) - fixação com espuma expansiva</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>un</t>
         </is>
       </c>
       <c r="D13" s="25" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="E13" s="26" t="n">
-        <v>120000</v>
+        <v>2575.52</v>
       </c>
       <c r="F13" s="27" t="n">
-        <v>120000</v>
+        <v>118473.92</v>
       </c>
       <c r="G13" s="23" t="n">
         <v>1</v>
@@ -4056,7 +3936,7 @@
       </c>
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>Porta de madeira- correr (trilho lateral) - folha leve/média - 70x210cm (kit completo) - fixação com espuma expansiva</t>
+          <t>Porta de madeira- correr - folha leve/média - 80x210cm (kit completo) - fixação com espuma expansiva</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -4065,13 +3945,13 @@
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>2575.52</v>
+        <v>2421.42</v>
       </c>
       <c r="F14" s="27" t="n">
-        <v>118473.92</v>
+        <v>38742.72</v>
       </c>
       <c r="G14" s="23" t="n">
         <v>1</v>
@@ -4088,22 +3968,22 @@
       </c>
       <c r="B15" s="24" t="inlineStr">
         <is>
-          <t>Ensaio de guarda corpo</t>
+          <t>Esquadrias Metálicas - Porta Corta Fogo P90 90x210 - fornecimento e instalacao</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>un</t>
         </is>
       </c>
       <c r="D15" s="25" t="n">
-        <v>1</v>
+        <v>19.5</v>
       </c>
       <c r="E15" s="26" t="n">
-        <v>57300</v>
+        <v>1433</v>
       </c>
       <c r="F15" s="27" t="n">
-        <v>57300</v>
+        <v>27943.5</v>
       </c>
       <c r="G15" s="23" t="n">
         <v>1</v>
@@ -4120,22 +4000,22 @@
       </c>
       <c r="B16" s="24" t="inlineStr">
         <is>
-          <t>Laudo de estanqueidade das esquadrias</t>
+          <t>Rodapé em alumínio, altura 3cm</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D16" s="25" t="n">
-        <v>1</v>
+        <v>392.97</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>41300</v>
+        <v>65.801</v>
       </c>
       <c r="F16" s="27" t="n">
-        <v>41300</v>
+        <v>25857.81897</v>
       </c>
       <c r="G16" s="23" t="n">
         <v>1</v>
@@ -4152,7 +4032,7 @@
       </c>
       <c r="B17" s="24" t="inlineStr">
         <is>
-          <t>Porta de madeira- correr - folha leve/média - 80x210cm (kit completo) - fixação com espuma expansiva</t>
+          <t>Porta de madeira- abrir - folha leve/média - 80x210cm (kit completo) - fixação com espuma expansiva</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -4161,13 +4041,13 @@
         </is>
       </c>
       <c r="D17" s="25" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E17" s="26" t="n">
-        <v>2421.42</v>
+        <v>1711</v>
       </c>
       <c r="F17" s="27" t="n">
-        <v>38742.72</v>
+        <v>23954</v>
       </c>
       <c r="G17" s="23" t="n">
         <v>1</v>
@@ -4184,7 +4064,7 @@
       </c>
       <c r="B18" s="24" t="inlineStr">
         <is>
-          <t>Esquadrias Metálicas - Porta Corta Fogo P90 90x210 - fornecimento e instalacao</t>
+          <t>Porta de madeira- abrir - folha leve/média - 60x210cm (kit completo) - fixação com espuma expansiva</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -4193,13 +4073,13 @@
         </is>
       </c>
       <c r="D18" s="25" t="n">
-        <v>19.5</v>
+        <v>7</v>
       </c>
       <c r="E18" s="26" t="n">
-        <v>1433</v>
+        <v>1711</v>
       </c>
       <c r="F18" s="27" t="n">
-        <v>27943.5</v>
+        <v>11977</v>
       </c>
       <c r="G18" s="23" t="n">
         <v>1</v>
@@ -4216,22 +4096,22 @@
       </c>
       <c r="B19" s="24" t="inlineStr">
         <is>
-          <t>Rodapé em alumínio, altura 3cm</t>
+          <t>Porta de madeira- abrir - folha leve/média - 90x210cm (kit completo) - fixação com espuma expansiva</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>un</t>
         </is>
       </c>
       <c r="D19" s="25" t="n">
-        <v>392.97</v>
+        <v>5</v>
       </c>
       <c r="E19" s="26" t="n">
-        <v>65.801</v>
+        <v>1811</v>
       </c>
       <c r="F19" s="27" t="n">
-        <v>25857.81897</v>
+        <v>9055</v>
       </c>
       <c r="G19" s="23" t="n">
         <v>1</v>
@@ -4248,22 +4128,22 @@
       </c>
       <c r="B20" s="24" t="inlineStr">
         <is>
-          <t>Projeto De Esquadrias</t>
+          <t>Porta de madeira- abrir - folha leve/média - 70x210cm (kit completo) - fixação com espuma expansiva</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>un</t>
         </is>
       </c>
       <c r="D20" s="25" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E20" s="26" t="n">
-        <v>24730.92</v>
+        <v>1711</v>
       </c>
       <c r="F20" s="27" t="n">
-        <v>24730.92</v>
+        <v>8555</v>
       </c>
       <c r="G20" s="23" t="n">
         <v>1</v>
@@ -4280,7 +4160,7 @@
       </c>
       <c r="B21" s="24" t="inlineStr">
         <is>
-          <t>Porta de madeira- abrir - folha leve/média - 80x210cm (kit completo) - fixação com espuma expansiva</t>
+          <t>Esquadrias Metálicas - Alçapão 80x80 - fornecimento e instalacao</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -4289,13 +4169,13 @@
         </is>
       </c>
       <c r="D21" s="25" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E21" s="26" t="n">
-        <v>1711</v>
+        <v>973.2828</v>
       </c>
       <c r="F21" s="27" t="n">
-        <v>23954</v>
+        <v>7786.2624</v>
       </c>
       <c r="G21" s="23" t="n">
         <v>1</v>
@@ -4312,7 +4192,7 @@
       </c>
       <c r="B22" s="24" t="inlineStr">
         <is>
-          <t>Porta de madeira- abrir - folha leve/média - 60x210cm (kit completo) - fixação com espuma expansiva</t>
+          <t>Porta de madeira- pivotante - folha leve/média - 153x210cm (kit completo) - fixação com espuma expansiva</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -4321,13 +4201,13 @@
         </is>
       </c>
       <c r="D22" s="25" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E22" s="26" t="n">
-        <v>1711</v>
+        <v>2266.9</v>
       </c>
       <c r="F22" s="27" t="n">
-        <v>11977</v>
+        <v>2266.9</v>
       </c>
       <c r="G22" s="23" t="n">
         <v>1</v>
@@ -4344,155 +4224,27 @@
       </c>
       <c r="B23" s="24" t="inlineStr">
         <is>
-          <t>Porta de madeira- abrir - folha leve/média - 90x210cm (kit completo) - fixação com espuma expansiva</t>
+          <t>Moldura em alumínio para churrasqueiras - fornecimento e instalação</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D23" s="25" t="n">
-        <v>5</v>
+        <v>17.2</v>
       </c>
       <c r="E23" s="26" t="n">
-        <v>1811</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="F23" s="27" t="n">
-        <v>9055</v>
+        <v>1477.48</v>
       </c>
       <c r="G23" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H23" s="24" t="inlineStr">
-        <is>
-          <t>fg-scenarium</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="23" t="n">
-        <v>20</v>
-      </c>
-      <c r="B24" s="24" t="inlineStr">
-        <is>
-          <t>Porta de madeira- abrir - folha leve/média - 70x210cm (kit completo) - fixação com espuma expansiva</t>
-        </is>
-      </c>
-      <c r="C24" s="23" t="inlineStr">
-        <is>
-          <t>un</t>
-        </is>
-      </c>
-      <c r="D24" s="25" t="n">
-        <v>5</v>
-      </c>
-      <c r="E24" s="26" t="n">
-        <v>1711</v>
-      </c>
-      <c r="F24" s="27" t="n">
-        <v>8555</v>
-      </c>
-      <c r="G24" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" s="24" t="inlineStr">
-        <is>
-          <t>fg-scenarium</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="23" t="n">
-        <v>21</v>
-      </c>
-      <c r="B25" s="24" t="inlineStr">
-        <is>
-          <t>Esquadrias Metálicas - Alçapão 80x80 - fornecimento e instalacao</t>
-        </is>
-      </c>
-      <c r="C25" s="23" t="inlineStr">
-        <is>
-          <t>un</t>
-        </is>
-      </c>
-      <c r="D25" s="25" t="n">
-        <v>8</v>
-      </c>
-      <c r="E25" s="26" t="n">
-        <v>973.2828</v>
-      </c>
-      <c r="F25" s="27" t="n">
-        <v>7786.2624</v>
-      </c>
-      <c r="G25" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" s="24" t="inlineStr">
-        <is>
-          <t>fg-scenarium</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="23" t="n">
-        <v>22</v>
-      </c>
-      <c r="B26" s="24" t="inlineStr">
-        <is>
-          <t>Porta de madeira- pivotante - folha leve/média - 153x210cm (kit completo) - fixação com espuma expansiva</t>
-        </is>
-      </c>
-      <c r="C26" s="23" t="inlineStr">
-        <is>
-          <t>un</t>
-        </is>
-      </c>
-      <c r="D26" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" s="26" t="n">
-        <v>2266.9</v>
-      </c>
-      <c r="F26" s="27" t="n">
-        <v>2266.9</v>
-      </c>
-      <c r="G26" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" s="24" t="inlineStr">
-        <is>
-          <t>fg-scenarium</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="23" t="n">
-        <v>23</v>
-      </c>
-      <c r="B27" s="24" t="inlineStr">
-        <is>
-          <t>Moldura em alumínio para churrasqueiras - fornecimento e instalação</t>
-        </is>
-      </c>
-      <c r="C27" s="23" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D27" s="25" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="E27" s="26" t="n">
-        <v>85.90000000000001</v>
-      </c>
-      <c r="F27" s="27" t="n">
-        <v>1477.48</v>
-      </c>
-      <c r="G27" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" s="24" t="inlineStr">
         <is>
           <t>fg-scenarium</t>
         </is>
@@ -4951,7 +4703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -5047,102 +4799,6 @@
         <v>1</v>
       </c>
       <c r="H5" s="24" t="inlineStr">
-        <is>
-          <t>fg-scenarium</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="24" t="inlineStr">
-        <is>
-          <t>Projeto Arquitetônico De Fachada</t>
-        </is>
-      </c>
-      <c r="C6" s="23" t="inlineStr">
-        <is>
-          <t>vb</t>
-        </is>
-      </c>
-      <c r="D6" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="26" t="n">
-        <v>61810.1</v>
-      </c>
-      <c r="F6" s="27" t="n">
-        <v>61810.1</v>
-      </c>
-      <c r="G6" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" s="24" t="inlineStr">
-        <is>
-          <t>fg-scenarium</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="24" t="inlineStr">
-        <is>
-          <t>Consultoria Técnica De Fachada</t>
-        </is>
-      </c>
-      <c r="C7" s="23" t="inlineStr">
-        <is>
-          <t>vb</t>
-        </is>
-      </c>
-      <c r="D7" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="26" t="n">
-        <v>18120.54</v>
-      </c>
-      <c r="F7" s="27" t="n">
-        <v>18120.54</v>
-      </c>
-      <c r="G7" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="24" t="inlineStr">
-        <is>
-          <t>fg-scenarium</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="24" t="inlineStr">
-        <is>
-          <t>Ensaio de arrancamento de fachada</t>
-        </is>
-      </c>
-      <c r="C8" s="23" t="inlineStr">
-        <is>
-          <t>vb</t>
-        </is>
-      </c>
-      <c r="D8" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="26" t="n">
-        <v>11040</v>
-      </c>
-      <c r="F8" s="27" t="n">
-        <v>11040</v>
-      </c>
-      <c r="G8" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="24" t="inlineStr">
         <is>
           <t>fg-scenarium</t>
         </is>
@@ -5239,29 +4895,25 @@
       </c>
       <c r="B5" s="24" t="inlineStr">
         <is>
-          <t>Mobiliário e decoração interna</t>
-        </is>
-      </c>
-      <c r="C5" s="23" t="inlineStr">
-        <is>
-          <t>vb</t>
-        </is>
-      </c>
+          <t>Esteira profissional touch Adidas</t>
+        </is>
+      </c>
+      <c r="C5" s="23" t="inlineStr"/>
       <c r="D5" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E5" s="26" t="n">
-        <v>6808330.41</v>
+        <v>20000</v>
       </c>
       <c r="F5" s="27" t="n">
-        <v>6808330.41</v>
+        <v>60000</v>
       </c>
       <c r="G5" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H5" s="24" t="inlineStr">
         <is>
-          <t>fg-scenarium</t>
+          <t>beco-castelo-chateau-de-versailes</t>
         </is>
       </c>
     </row>
@@ -5271,29 +4923,25 @@
       </c>
       <c r="B6" s="24" t="inlineStr">
         <is>
-          <t>Paisagismo</t>
-        </is>
-      </c>
-      <c r="C6" s="23" t="inlineStr">
-        <is>
-          <t>vb</t>
-        </is>
-      </c>
+          <t>Área:</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr"/>
       <c r="D6" s="25" t="n">
-        <v>1</v>
+        <v>16.77</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>1317607.74</v>
+        <v>2217.906336088155</v>
       </c>
       <c r="F6" s="27" t="n">
-        <v>1317607.74</v>
+        <v>37194.28925619835</v>
       </c>
       <c r="G6" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H6" s="24" t="inlineStr">
         <is>
-          <t>fg-scenarium</t>
+          <t>beco-castelo-chateau-de-versailes</t>
         </is>
       </c>
     </row>
@@ -5303,29 +4951,25 @@
       </c>
       <c r="B7" s="24" t="inlineStr">
         <is>
-          <t>Limpeza Final</t>
-        </is>
-      </c>
-      <c r="C7" s="23" t="inlineStr">
-        <is>
-          <t>vb</t>
-        </is>
-      </c>
+          <t>Mesa de jantar Hiller</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr"/>
       <c r="D7" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" s="26" t="n">
-        <v>634166.55</v>
+        <v>15531</v>
       </c>
       <c r="F7" s="27" t="n">
-        <v>634166.55</v>
+        <v>31062</v>
       </c>
       <c r="G7" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H7" s="24" t="inlineStr">
         <is>
-          <t>fg-scenarium</t>
+          <t>beco-castelo-chateau-de-versailes</t>
         </is>
       </c>
     </row>
@@ -5335,29 +4979,25 @@
       </c>
       <c r="B8" s="24" t="inlineStr">
         <is>
-          <t>Mobiliário e decoração externa</t>
-        </is>
-      </c>
-      <c r="C8" s="23" t="inlineStr">
-        <is>
-          <t>vb</t>
-        </is>
-      </c>
+          <t>Espreguiçadeira Duma - Brisa Casa</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr"/>
       <c r="D8" s="25" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>397745.04</v>
+        <v>4180</v>
       </c>
       <c r="F8" s="27" t="n">
-        <v>397745.04</v>
+        <v>25080</v>
       </c>
       <c r="G8" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H8" s="24" t="inlineStr">
         <is>
-          <t>fg-scenarium</t>
+          <t>beco-castelo-chateau-de-versailes</t>
         </is>
       </c>
     </row>
@@ -5367,29 +5007,25 @@
       </c>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>Mobiliário e equipamentos de apoio a obra</t>
-        </is>
-      </c>
-      <c r="C9" s="23" t="inlineStr">
-        <is>
-          <t>vb</t>
-        </is>
-      </c>
+          <t>Cadeira Évora com braço</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr"/>
       <c r="D9" s="25" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E9" s="26" t="n">
-        <v>83300</v>
+        <v>4000</v>
       </c>
       <c r="F9" s="27" t="n">
-        <v>83300</v>
+        <v>24000</v>
       </c>
       <c r="G9" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H9" s="24" t="inlineStr">
         <is>
-          <t>fg-scenarium</t>
+          <t>beco-castelo-chateau-de-versailes</t>
         </is>
       </c>
     </row>
@@ -5399,18 +5035,18 @@
       </c>
       <c r="B10" s="24" t="inlineStr">
         <is>
-          <t>Esteira profissional touch Adidas</t>
+          <t>Cadeira Rio sem braço - Studio Ambientes</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr"/>
       <c r="D10" s="25" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="E10" s="26" t="n">
-        <v>20000</v>
+        <v>900</v>
       </c>
       <c r="F10" s="27" t="n">
-        <v>60000</v>
+        <v>21600</v>
       </c>
       <c r="G10" s="23" t="n">
         <v>1</v>
@@ -5427,18 +5063,18 @@
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>Área:</t>
+          <t>Mesa Poker Arizona redondo</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr"/>
       <c r="D11" s="25" t="n">
-        <v>16.77</v>
+        <v>2</v>
       </c>
       <c r="E11" s="26" t="n">
-        <v>2217.906336088155</v>
+        <v>10000</v>
       </c>
       <c r="F11" s="27" t="n">
-        <v>37194.28925619835</v>
+        <v>20000</v>
       </c>
       <c r="G11" s="23" t="n">
         <v>1</v>
@@ -5455,18 +5091,18 @@
       </c>
       <c r="B12" s="24" t="inlineStr">
         <is>
-          <t>Playground de madeira casinha com ponte</t>
+          <t>Banco Scala - De Lazzari</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr"/>
       <c r="D12" s="25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>34560</v>
+        <v>4500</v>
       </c>
       <c r="F12" s="27" t="n">
-        <v>34560</v>
+        <v>18000</v>
       </c>
       <c r="G12" s="23" t="n">
         <v>1</v>
@@ -5483,18 +5119,18 @@
       </c>
       <c r="B13" s="24" t="inlineStr">
         <is>
-          <t>Marcenaria</t>
+          <t>Mesa com tampo quadrado - Studio Ambientes</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr"/>
       <c r="D13" s="25" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E13" s="26" t="n">
-        <v>33540</v>
+        <v>2500</v>
       </c>
       <c r="F13" s="27" t="n">
-        <v>33540</v>
+        <v>15000</v>
       </c>
       <c r="G13" s="23" t="n">
         <v>1</v>
@@ -5511,18 +5147,18 @@
       </c>
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>Mesa de jantar Hiller</t>
+          <t>Vaso caixa alta M</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr"/>
       <c r="D14" s="25" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>15531</v>
+        <v>500</v>
       </c>
       <c r="F14" s="27" t="n">
-        <v>31062</v>
+        <v>12500</v>
       </c>
       <c r="G14" s="23" t="n">
         <v>1</v>
@@ -5539,22 +5175,22 @@
       </c>
       <c r="B15" s="24" t="inlineStr">
         <is>
-          <t>Projeto De Paisagismo</t>
+          <t>Manutenção Tapume e Calçada</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>mes</t>
         </is>
       </c>
       <c r="D15" s="25" t="n">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="E15" s="26" t="n">
-        <v>28539.04</v>
+        <v>250</v>
       </c>
       <c r="F15" s="27" t="n">
-        <v>28539.04</v>
+        <v>12250</v>
       </c>
       <c r="G15" s="23" t="n">
         <v>1</v>
@@ -5571,18 +5207,18 @@
       </c>
       <c r="B16" s="24" t="inlineStr">
         <is>
-          <t>Espreguiçadeira Duma - Brisa Casa</t>
+          <t>Poltrona Yan</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr"/>
       <c r="D16" s="25" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>4180</v>
+        <v>5896</v>
       </c>
       <c r="F16" s="27" t="n">
-        <v>25080</v>
+        <v>11792</v>
       </c>
       <c r="G16" s="23" t="n">
         <v>1</v>
@@ -5599,18 +5235,18 @@
       </c>
       <c r="B17" s="24" t="inlineStr">
         <is>
-          <t>Sofá Pedras - Casa de Alessa</t>
+          <t>Espreguiçadeira Santorini</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr"/>
       <c r="D17" s="25" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E17" s="26" t="n">
-        <v>25000</v>
+        <v>1200</v>
       </c>
       <c r="F17" s="27" t="n">
-        <v>25000</v>
+        <v>9600</v>
       </c>
       <c r="G17" s="23" t="n">
         <v>1</v>
@@ -5627,18 +5263,18 @@
       </c>
       <c r="B18" s="24" t="inlineStr">
         <is>
-          <t>Sofá Arc</t>
+          <t>Sofá linha Austin Up</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr"/>
       <c r="D18" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" s="26" t="n">
-        <v>25000</v>
+        <v>4500</v>
       </c>
       <c r="F18" s="27" t="n">
-        <v>25000</v>
+        <v>9000</v>
       </c>
       <c r="G18" s="23" t="n">
         <v>1</v>
@@ -5655,18 +5291,18 @@
       </c>
       <c r="B19" s="24" t="inlineStr">
         <is>
-          <t>Sofá curvo Andros</t>
+          <t>Kit toalhas</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr"/>
       <c r="D19" s="25" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E19" s="26" t="n">
-        <v>25000</v>
+        <v>500</v>
       </c>
       <c r="F19" s="27" t="n">
-        <v>25000</v>
+        <v>7500</v>
       </c>
       <c r="G19" s="23" t="n">
         <v>1</v>
@@ -5683,25 +5319,29 @@
       </c>
       <c r="B20" s="24" t="inlineStr">
         <is>
-          <t>Cadeira Évora com braço</t>
-        </is>
-      </c>
-      <c r="C20" s="23" t="inlineStr"/>
+          <t>Calçada/passeio em piso intertravado, com bloco retangular cor natural de 20x10cm, espessura 8cm</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
       <c r="D20" s="25" t="n">
-        <v>6</v>
+        <v>76.45</v>
       </c>
       <c r="E20" s="26" t="n">
-        <v>4000</v>
+        <v>94.6092</v>
       </c>
       <c r="F20" s="27" t="n">
-        <v>24000</v>
+        <v>7232.87334</v>
       </c>
       <c r="G20" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H20" s="24" t="inlineStr">
         <is>
-          <t>beco-castelo-chateau-de-versailes</t>
+          <t>fg-scenarium</t>
         </is>
       </c>
     </row>
@@ -5711,18 +5351,18 @@
       </c>
       <c r="B21" s="24" t="inlineStr">
         <is>
-          <t>Cadeira Rio sem braço - Studio Ambientes</t>
+          <t>Poltrona Blad</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr"/>
       <c r="D21" s="25" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="E21" s="26" t="n">
-        <v>900</v>
+        <v>1800</v>
       </c>
       <c r="F21" s="27" t="n">
-        <v>21600</v>
+        <v>7200</v>
       </c>
       <c r="G21" s="23" t="n">
         <v>1</v>
@@ -5739,18 +5379,18 @@
       </c>
       <c r="B22" s="24" t="inlineStr">
         <is>
-          <t>Mesa Poker Arizona redondo</t>
+          <t>Cadeira bloo</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr"/>
       <c r="D22" s="25" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E22" s="26" t="n">
-        <v>10000</v>
+        <v>850</v>
       </c>
       <c r="F22" s="27" t="n">
-        <v>20000</v>
+        <v>6800</v>
       </c>
       <c r="G22" s="23" t="n">
         <v>1</v>
@@ -5767,25 +5407,29 @@
       </c>
       <c r="B23" s="24" t="inlineStr">
         <is>
-          <t>Banco Scala - De Lazzari</t>
-        </is>
-      </c>
-      <c r="C23" s="23" t="inlineStr"/>
+          <t>Calçada provisória, execuão de piso intertravado</t>
+        </is>
+      </c>
+      <c r="C23" s="23" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
       <c r="D23" s="25" t="n">
-        <v>4</v>
+        <v>65.97</v>
       </c>
       <c r="E23" s="26" t="n">
-        <v>4500</v>
+        <v>102.777</v>
       </c>
       <c r="F23" s="27" t="n">
-        <v>18000</v>
+        <v>6780.19869</v>
       </c>
       <c r="G23" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H23" s="24" t="inlineStr">
         <is>
-          <t>beco-castelo-chateau-de-versailes</t>
+          <t>fg-scenarium</t>
         </is>
       </c>
     </row>
@@ -5795,18 +5439,18 @@
       </c>
       <c r="B24" s="24" t="inlineStr">
         <is>
-          <t>Mesa com tampo quadrado - Studio Ambientes</t>
+          <t>Jogo Jantar Chá Bar Hotel 30 Peças Porcelana Germer 6 Pessoas</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr"/>
       <c r="D24" s="25" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="E24" s="26" t="n">
-        <v>2500</v>
+        <v>320</v>
       </c>
       <c r="F24" s="27" t="n">
-        <v>15000</v>
+        <v>6720</v>
       </c>
       <c r="G24" s="23" t="n">
         <v>1</v>
@@ -5823,18 +5467,18 @@
       </c>
       <c r="B25" s="24" t="inlineStr">
         <is>
-          <t>Mesa sinuca Michigan semioficial</t>
+          <t>Tapete retangular Sisal sintetico</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr"/>
       <c r="D25" s="25" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E25" s="26" t="n">
-        <v>15000</v>
+        <v>4250</v>
       </c>
       <c r="F25" s="27" t="n">
-        <v>15000</v>
+        <v>6375</v>
       </c>
       <c r="G25" s="23" t="n">
         <v>1</v>
@@ -5851,18 +5495,18 @@
       </c>
       <c r="B26" s="24" t="inlineStr">
         <is>
-          <t>Vaso caixa alta M</t>
+          <t>Cadeira coelho madeira e palha</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr"/>
       <c r="D26" s="25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E26" s="26" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="F26" s="27" t="n">
-        <v>12500</v>
+        <v>6000</v>
       </c>
       <c r="G26" s="23" t="n">
         <v>1</v>
@@ -5879,29 +5523,25 @@
       </c>
       <c r="B27" s="24" t="inlineStr">
         <is>
-          <t>Manutenção Tapume e Calçada</t>
-        </is>
-      </c>
-      <c r="C27" s="23" t="inlineStr">
-        <is>
-          <t>mes</t>
-        </is>
-      </c>
+          <t>Jardineira alta M</t>
+        </is>
+      </c>
+      <c r="C27" s="23" t="inlineStr"/>
       <c r="D27" s="25" t="n">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="E27" s="26" t="n">
-        <v>250</v>
+        <v>450</v>
       </c>
       <c r="F27" s="27" t="n">
-        <v>12250</v>
+        <v>5850</v>
       </c>
       <c r="G27" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H27" s="24" t="inlineStr">
         <is>
-          <t>fg-scenarium</t>
+          <t>beco-castelo-chateau-de-versailes</t>
         </is>
       </c>
     </row>
@@ -5911,18 +5551,18 @@
       </c>
       <c r="B28" s="24" t="inlineStr">
         <is>
-          <t>Mega cross com Smith titanium Special</t>
+          <t>Banqueta Drop</t>
         </is>
       </c>
       <c r="C28" s="23" t="inlineStr"/>
       <c r="D28" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E28" s="26" t="n">
-        <v>12000</v>
+        <v>1800</v>
       </c>
       <c r="F28" s="27" t="n">
-        <v>12000</v>
+        <v>5400</v>
       </c>
       <c r="G28" s="23" t="n">
         <v>1</v>
@@ -5939,7 +5579,7 @@
       </c>
       <c r="B29" s="24" t="inlineStr">
         <is>
-          <t>Poltrona Yan</t>
+          <t>Chaise sofia</t>
         </is>
       </c>
       <c r="C29" s="23" t="inlineStr"/>
@@ -5947,10 +5587,10 @@
         <v>2</v>
       </c>
       <c r="E29" s="26" t="n">
-        <v>5896</v>
+        <v>2530</v>
       </c>
       <c r="F29" s="27" t="n">
-        <v>11792</v>
+        <v>5060</v>
       </c>
       <c r="G29" s="23" t="n">
         <v>1</v>
@@ -5967,18 +5607,18 @@
       </c>
       <c r="B30" s="24" t="inlineStr">
         <is>
-          <t>Espreguiçadeira Santorini</t>
+          <t>Exposito vertical 414L - Gelopar</t>
         </is>
       </c>
       <c r="C30" s="23" t="inlineStr"/>
       <c r="D30" s="25" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E30" s="26" t="n">
-        <v>1200</v>
+        <v>2500</v>
       </c>
       <c r="F30" s="27" t="n">
-        <v>9600</v>
+        <v>5000</v>
       </c>
       <c r="G30" s="23" t="n">
         <v>1</v>
@@ -5995,18 +5635,18 @@
       </c>
       <c r="B31" s="24" t="inlineStr">
         <is>
-          <t>Sofá linha Austin Up</t>
+          <t>Carro de Chá Dudi - Studio ambientes</t>
         </is>
       </c>
       <c r="C31" s="23" t="inlineStr"/>
       <c r="D31" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E31" s="26" t="n">
-        <v>4500</v>
+        <v>5000</v>
       </c>
       <c r="F31" s="27" t="n">
-        <v>9000</v>
+        <v>5000</v>
       </c>
       <c r="G31" s="23" t="n">
         <v>1</v>
@@ -6023,7 +5663,7 @@
       </c>
       <c r="B32" s="24" t="inlineStr">
         <is>
-          <t>Apador Bar Bossa - Realwood</t>
+          <t>Forno de embutir elétrico 67L - Brastemp</t>
         </is>
       </c>
       <c r="C32" s="23" t="inlineStr"/>
@@ -6031,10 +5671,10 @@
         <v>1</v>
       </c>
       <c r="E32" s="26" t="n">
-        <v>8569</v>
+        <v>5000</v>
       </c>
       <c r="F32" s="27" t="n">
-        <v>8569</v>
+        <v>5000</v>
       </c>
       <c r="G32" s="23" t="n">
         <v>1</v>
@@ -6051,7 +5691,7 @@
       </c>
       <c r="B33" s="24" t="inlineStr">
         <is>
-          <t>Bike horizontal Adidas</t>
+          <t>Supino regulavel Titanium Special</t>
         </is>
       </c>
       <c r="C33" s="23" t="inlineStr"/>
@@ -6059,10 +5699,10 @@
         <v>1</v>
       </c>
       <c r="E33" s="26" t="n">
-        <v>8000</v>
+        <v>5000</v>
       </c>
       <c r="F33" s="27" t="n">
-        <v>8000</v>
+        <v>5000</v>
       </c>
       <c r="G33" s="23" t="n">
         <v>1</v>
@@ -6079,7 +5719,7 @@
       </c>
       <c r="B34" s="24" t="inlineStr">
         <is>
-          <t>Cadeira extensora/flexora conjunto Titanuium Special</t>
+          <t>Eliptico Adidas</t>
         </is>
       </c>
       <c r="C34" s="23" t="inlineStr"/>
@@ -6087,10 +5727,10 @@
         <v>1</v>
       </c>
       <c r="E34" s="26" t="n">
-        <v>7800</v>
+        <v>5000</v>
       </c>
       <c r="F34" s="27" t="n">
-        <v>7800</v>
+        <v>5000</v>
       </c>
       <c r="G34" s="23" t="n">
         <v>1</v>
@@ -6187,36 +5827,12 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="24" t="inlineStr">
-        <is>
-          <t>Imprevistos e contingências</t>
-        </is>
-      </c>
-      <c r="C5" s="23" t="inlineStr">
-        <is>
-          <t>vb</t>
-        </is>
-      </c>
-      <c r="D5" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="26" t="n">
-        <v>3051396.927</v>
-      </c>
-      <c r="F5" s="27" t="n">
-        <v>3051396.927</v>
-      </c>
-      <c r="G5" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="24" t="inlineStr">
-        <is>
-          <t>fg-scenarium</t>
-        </is>
-      </c>
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>(sem detalhamento granular nos similares — usar valor agregado acima)</t>
+        </is>
+      </c>
+      <c r="B5" s="28" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6234,7 +5850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -6341,123 +5957,27 @@
       </c>
       <c r="B6" s="24" t="inlineStr">
         <is>
-          <t>Construções provisórias (escritório, almoxarifado, vestiário e baias de material)</t>
+          <t>Equipe Indireta - Auxiliar de Almoxarife</t>
         </is>
       </c>
       <c r="C6" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>mes</t>
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>198400.54</v>
+        <v>4512.95</v>
       </c>
       <c r="F6" s="27" t="n">
-        <v>198400.54</v>
+        <v>185030.95</v>
       </c>
       <c r="G6" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H6" s="24" t="inlineStr">
-        <is>
-          <t>fg-scenarium</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="24" t="inlineStr">
-        <is>
-          <t>Equipe Indireta - Auxiliar de Almoxarife</t>
-        </is>
-      </c>
-      <c r="C7" s="23" t="inlineStr">
-        <is>
-          <t>mes</t>
-        </is>
-      </c>
-      <c r="D7" s="25" t="n">
-        <v>41</v>
-      </c>
-      <c r="E7" s="26" t="n">
-        <v>4512.95</v>
-      </c>
-      <c r="F7" s="27" t="n">
-        <v>185030.95</v>
-      </c>
-      <c r="G7" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="24" t="inlineStr">
-        <is>
-          <t>fg-scenarium</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="24" t="inlineStr">
-        <is>
-          <t>Equipamentos de Proteção Individual - EPI</t>
-        </is>
-      </c>
-      <c r="C8" s="23" t="inlineStr">
-        <is>
-          <t>vb</t>
-        </is>
-      </c>
-      <c r="D8" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="26" t="n">
-        <v>95500</v>
-      </c>
-      <c r="F8" s="27" t="n">
-        <v>95500</v>
-      </c>
-      <c r="G8" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="24" t="inlineStr">
-        <is>
-          <t>fg-scenarium</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="24" t="inlineStr">
-        <is>
-          <t>Sala do cliente (incluso EPIs, equipamentos, parte civil e decoração)</t>
-        </is>
-      </c>
-      <c r="C9" s="23" t="inlineStr">
-        <is>
-          <t>vb</t>
-        </is>
-      </c>
-      <c r="D9" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="26" t="n">
-        <v>20016.93</v>
-      </c>
-      <c r="F9" s="27" t="n">
-        <v>20016.93</v>
-      </c>
-      <c r="G9" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="24" t="inlineStr">
         <is>
           <t>fg-scenarium</t>
         </is>
@@ -6530,7 +6050,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="28" t="n">
+      <c r="A4" s="29" t="n">
         <v>1</v>
       </c>
       <c r="B4" s="18" t="inlineStr">
@@ -6538,19 +6058,19 @@
           <t>beco-castelo-chateau-de-versailes</t>
         </is>
       </c>
-      <c r="C4" s="29" t="n">
+      <c r="C4" s="30" t="n">
         <v>32507.25</v>
       </c>
-      <c r="D4" s="28" t="n">
+      <c r="D4" s="29" t="n">
         <v>142</v>
       </c>
-      <c r="E4" s="30" t="n">
+      <c r="E4" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="31" t="n"/>
+      <c r="F4" s="32" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="28" t="n">
+      <c r="A5" s="29" t="n">
         <v>2</v>
       </c>
       <c r="B5" s="18" t="inlineStr">
@@ -6558,19 +6078,19 @@
           <t>f-nogueira-wpr</t>
         </is>
       </c>
-      <c r="C5" s="29" t="n">
+      <c r="C5" s="30" t="n">
         <v>37483.31</v>
       </c>
-      <c r="D5" s="28" t="n"/>
-      <c r="E5" s="30" t="n">
+      <c r="D5" s="29" t="n"/>
+      <c r="E5" s="31" t="n">
         <v>2549.1</v>
       </c>
-      <c r="F5" s="31" t="n">
+      <c r="F5" s="32" t="n">
         <v>95548670.14</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="28" t="n">
+      <c r="A6" s="29" t="n">
         <v>3</v>
       </c>
       <c r="B6" s="18" t="inlineStr">
@@ -6578,19 +6098,19 @@
           <t>fg-scenarium</t>
         </is>
       </c>
-      <c r="C6" s="29" t="n">
+      <c r="C6" s="30" t="n">
         <v>42277.77</v>
       </c>
-      <c r="D6" s="28" t="n"/>
-      <c r="E6" s="30" t="n">
+      <c r="D6" s="29" t="n"/>
+      <c r="E6" s="31" t="n">
         <v>4888.48</v>
       </c>
-      <c r="F6" s="31" t="n">
+      <c r="F6" s="32" t="n">
         <v>206674002.44</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="28" t="n">
+      <c r="A7" s="29" t="n">
         <v>4</v>
       </c>
       <c r="B7" s="18" t="inlineStr">
@@ -6598,19 +6118,19 @@
           <t>colline-de-france-colline-de-france</t>
         </is>
       </c>
-      <c r="C7" s="29" t="n">
+      <c r="C7" s="30" t="n">
         <v>27559.45</v>
       </c>
-      <c r="D7" s="28" t="n"/>
-      <c r="E7" s="30" t="n">
+      <c r="D7" s="29" t="n"/>
+      <c r="E7" s="31" t="n">
         <v>5219.45</v>
       </c>
-      <c r="F7" s="31" t="n">
+      <c r="F7" s="32" t="n">
         <v>143845292.36</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="28" t="n">
+      <c r="A8" s="29" t="n">
         <v>5</v>
       </c>
       <c r="B8" s="18" t="inlineStr">
@@ -6618,14 +6138,14 @@
           <t>f-nogueira-soberano</t>
         </is>
       </c>
-      <c r="C8" s="29" t="n">
+      <c r="C8" s="30" t="n">
         <v>27247.73</v>
       </c>
-      <c r="D8" s="28" t="n"/>
-      <c r="E8" s="30" t="n">
+      <c r="D8" s="29" t="n"/>
+      <c r="E8" s="31" t="n">
         <v>2634.07</v>
       </c>
-      <c r="F8" s="31" t="n">
+      <c r="F8" s="32" t="n">
         <v>71772532.29000001</v>
       </c>
     </row>
@@ -7017,272 +6537,272 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="32" t="inlineStr">
+      <c r="A24" s="28" t="inlineStr">
         <is>
           <t>Lastro de concreto magro</t>
         </is>
       </c>
-      <c r="B24" s="32" t="inlineStr">
+      <c r="B24" s="28" t="inlineStr">
         <is>
           <t>aplicado em blocos de coroamento ou sapatas, espessura 5cm</t>
         </is>
       </c>
-      <c r="C24" s="32" t="inlineStr">
+      <c r="C24" s="28" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="32" t="inlineStr">
+      <c r="A25" s="28" t="inlineStr">
         <is>
           <t>Alvenaria de vedação</t>
         </is>
       </c>
-      <c r="B25" s="32" t="inlineStr">
+      <c r="B25" s="28" t="inlineStr">
         <is>
           <t>blocos cerâmicos furados na horizontal de 9x19x29, com argamassa 1:2</t>
         </is>
       </c>
-      <c r="C25" s="32" t="inlineStr">
+      <c r="C25" s="28" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="32" t="inlineStr">
+      <c r="A26" s="28" t="inlineStr">
         <is>
           <t>Geral</t>
         </is>
       </c>
-      <c r="B26" s="32" t="inlineStr">
+      <c r="B26" s="28" t="inlineStr">
         <is>
           <t>Fechamento em Light Steel Frame, com divisórias em Drywall</t>
         </is>
       </c>
-      <c r="C26" s="32" t="inlineStr">
+      <c r="C26" s="28" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="32" t="inlineStr">
+      <c r="A27" s="28" t="inlineStr">
         <is>
           <t>Lazer</t>
         </is>
       </c>
-      <c r="B27" s="32" t="inlineStr">
+      <c r="B27" s="28" t="inlineStr">
         <is>
           <t>Lazer com mais de 3.800 m², piscinas aquecidas e borda infinita, áreas comuns completas, infra automação, aspiração central, aquecedor de passagem.</t>
         </is>
       </c>
-      <c r="C27" s="32" t="inlineStr">
+      <c r="C27" s="28" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="32" t="inlineStr">
+      <c r="A28" s="28" t="inlineStr">
         <is>
           <t>Quantificação</t>
         </is>
       </c>
-      <c r="B28" s="32" t="inlineStr">
+      <c r="B28" s="28" t="inlineStr">
         <is>
           <t>Quantificação seguindo detalhamentos de projeto e resumo de quantitativos disponibilizados de cada torre; Demais quantidades estimadas devido ausência de detalhamentos extrapolando índ…os.</t>
         </is>
       </c>
-      <c r="C28" s="32" t="inlineStr">
+      <c r="C28" s="28" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="32" t="inlineStr">
+      <c r="A29" s="28" t="inlineStr">
         <is>
           <t>Cronograma</t>
         </is>
       </c>
-      <c r="B29" s="32" t="inlineStr">
+      <c r="B29" s="28" t="inlineStr">
         <is>
           <t>Custos consideram prazo de obra de 49 meses;</t>
         </is>
       </c>
-      <c r="C29" s="32" t="inlineStr">
+      <c r="C29" s="28" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="32" t="inlineStr">
+      <c r="A30" s="28" t="inlineStr">
         <is>
           <t>Terra</t>
         </is>
       </c>
-      <c r="B30" s="32" t="inlineStr">
+      <c r="B30" s="28" t="inlineStr">
         <is>
           <t>Limpeza de terreno mecanizada permanente; Terraplenagem considerando corte e reaterro em solo e rocha; Escavação e reaterro mecanizado de valas para blocos e baldrames; Apiloamento mecânico do solo para valas de infraestrutura; Movimentação de bota-fora para escavação do terreno, valas de infraestrutura e estacas, considerando 30% de empolamento;</t>
         </is>
       </c>
-      <c r="C30" s="32" t="inlineStr">
+      <c r="C30" s="28" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="32" t="inlineStr">
+      <c r="A31" s="28" t="inlineStr">
         <is>
           <t>Fundação</t>
         </is>
       </c>
-      <c r="B31" s="32" t="inlineStr">
+      <c r="B31" s="28" t="inlineStr">
         <is>
           <t>Concreto fck 40 MPa para estaca hélice, considerando perda de 20%; Argamassa para estaca raiz fck 30 MPa, considerando 30% de perda;</t>
         </is>
       </c>
-      <c r="C31" s="32" t="inlineStr">
+      <c r="C31" s="28" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="32" t="inlineStr">
+      <c r="A32" s="28" t="inlineStr">
         <is>
           <t>Contenção</t>
         </is>
       </c>
-      <c r="B32" s="32" t="inlineStr">
+      <c r="B32" s="28" t="inlineStr">
         <is>
           <t>Concreto fck 30 e 35 MPa em contenções, com consideração de 5% de perda e aditivo impermeabilizante;</t>
         </is>
       </c>
-      <c r="C32" s="32" t="inlineStr">
+      <c r="C32" s="28" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="32" t="inlineStr">
+      <c r="A33" s="28" t="inlineStr">
         <is>
           <t>MOVIMENTAÇÃO DE TERRA</t>
         </is>
       </c>
-      <c r="B33" s="32" t="inlineStr">
+      <c r="B33" s="28" t="inlineStr">
         <is>
           <t>402.746,20</t>
         </is>
       </c>
-      <c r="C33" s="32" t="inlineStr">
+      <c r="C33" s="28" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="32" t="inlineStr">
+      <c r="A34" s="28" t="inlineStr">
         <is>
           <t>INFRAESTRUTURA</t>
         </is>
       </c>
-      <c r="B34" s="32" t="inlineStr">
+      <c r="B34" s="28" t="inlineStr">
         <is>
           <t>1.817.696,57</t>
         </is>
       </c>
-      <c r="C34" s="32" t="inlineStr">
+      <c r="C34" s="28" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="32" t="inlineStr">
+      <c r="A35" s="28" t="inlineStr">
         <is>
           <t>SUPRAESTRUTURA</t>
         </is>
       </c>
-      <c r="B35" s="32" t="inlineStr">
+      <c r="B35" s="28" t="inlineStr">
         <is>
           <t>12.012.324,18</t>
         </is>
       </c>
-      <c r="C35" s="32" t="inlineStr">
+      <c r="C35" s="28" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="32" t="inlineStr">
+      <c r="A36" s="28" t="inlineStr">
         <is>
           <t>ALVENARIA, VEDAÇÕES E DIVISÓRIAS</t>
         </is>
       </c>
-      <c r="B36" s="32" t="inlineStr">
+      <c r="B36" s="28" t="inlineStr">
         <is>
           <t>1.630.504,11</t>
         </is>
       </c>
-      <c r="C36" s="32" t="inlineStr">
+      <c r="C36" s="28" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="32" t="inlineStr">
+      <c r="A37" s="28" t="inlineStr">
         <is>
           <t>SISTEMAS E INSTALAÇÕES ELÉTRICAS</t>
         </is>
       </c>
-      <c r="B37" s="32" t="inlineStr">
+      <c r="B37" s="28" t="inlineStr">
         <is>
           <t>4.313.372,95</t>
         </is>
       </c>
-      <c r="C37" s="32" t="inlineStr">
+      <c r="C37" s="28" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="32" t="inlineStr">
+      <c r="A38" s="28" t="inlineStr">
         <is>
           <t>SISTEMAS E INSTALAÇÕES HIDROSSANITÁRIAS E DRENAGEM</t>
         </is>
       </c>
-      <c r="B38" s="32" t="inlineStr">
+      <c r="B38" s="28" t="inlineStr">
         <is>
           <t>2.583.129,65</t>
         </is>
       </c>
-      <c r="C38" s="32" t="inlineStr">
+      <c r="C38" s="28" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="32" t="inlineStr">
+      <c r="A39" s="28" t="inlineStr">
         <is>
           <t>EQUIPAMENTOS E SISTEMAS ESPECIAIS</t>
         </is>
       </c>
-      <c r="B39" s="32" t="inlineStr">
+      <c r="B39" s="28" t="inlineStr">
         <is>
           <t>5.300.000,00</t>
         </is>
       </c>
-      <c r="C39" s="32" t="inlineStr">
+      <c r="C39" s="28" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
@@ -7303,7 +6823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -7506,59 +7026,27 @@
       </c>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>Projeto De Terraplenagem</t>
+          <t>Serviço de Terraplenagem / Espalhamento / Umedecimento / Compactação em Material de 1º Categoria - 95% PN - Aterro</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="D9" s="25" t="n">
-        <v>1</v>
+        <v>0.06</v>
       </c>
       <c r="E9" s="26" t="n">
-        <v>9385.58</v>
+        <v>9.09</v>
       </c>
       <c r="F9" s="27" t="n">
-        <v>9385.58</v>
+        <v>0.5454</v>
       </c>
       <c r="G9" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H9" s="24" t="inlineStr">
-        <is>
-          <t>fg-scenarium</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="23" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="24" t="inlineStr">
-        <is>
-          <t>Serviço de Terraplenagem / Espalhamento / Umedecimento / Compactação em Material de 1º Categoria - 95% PN - Aterro</t>
-        </is>
-      </c>
-      <c r="C10" s="23" t="inlineStr">
-        <is>
-          <t>m3</t>
-        </is>
-      </c>
-      <c r="D10" s="25" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E10" s="26" t="n">
-        <v>9.09</v>
-      </c>
-      <c r="F10" s="27" t="n">
-        <v>0.5454</v>
-      </c>
-      <c r="G10" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="24" t="inlineStr">
         <is>
           <t>fg-scenarium</t>
         </is>
@@ -7580,7 +7068,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -7719,22 +7207,22 @@
       </c>
       <c r="B7" s="24" t="inlineStr">
         <is>
-          <t>Infraestrutura e Equipamentos de Exaustão de Subsolo</t>
+          <t>Execucao Estaca Helice Continua 060Cm</t>
         </is>
       </c>
       <c r="C7" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D7" s="25" t="n">
-        <v>1</v>
+        <v>3996</v>
       </c>
       <c r="E7" s="26" t="n">
-        <v>637627</v>
+        <v>112.6</v>
       </c>
       <c r="F7" s="27" t="n">
-        <v>637627</v>
+        <v>449949.6</v>
       </c>
       <c r="G7" s="23" t="n">
         <v>1</v>
@@ -7751,22 +7239,22 @@
       </c>
       <c r="B8" s="24" t="inlineStr">
         <is>
-          <t>Infraestrutura de Climatização</t>
+          <t>Execucao Estaca Helice Continua 040Cm</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>1</v>
+        <v>1808</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>581280</v>
+        <v>101.44</v>
       </c>
       <c r="F8" s="27" t="n">
-        <v>581280</v>
+        <v>183403.52</v>
       </c>
       <c r="G8" s="23" t="n">
         <v>1</v>
@@ -7783,22 +7271,22 @@
       </c>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>Infraestrutura e Equipamentos de Exaustão para Ambientes Enclausurados</t>
+          <t>Serviço de Bota-fora - Valas de Infraestrutura</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="D9" s="25" t="n">
-        <v>1</v>
+        <v>3807.55</v>
       </c>
       <c r="E9" s="26" t="n">
-        <v>526655</v>
+        <v>45.45</v>
       </c>
       <c r="F9" s="27" t="n">
-        <v>526655</v>
+        <v>173053.1475</v>
       </c>
       <c r="G9" s="23" t="n">
         <v>1</v>
@@ -7815,22 +7303,22 @@
       </c>
       <c r="B10" s="24" t="inlineStr">
         <is>
-          <t>Execucao Estaca Helice Continua 060Cm</t>
+          <t>Serviço de Arrasamento Mecanizado de Estacas</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>un</t>
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>3996</v>
+        <v>518</v>
       </c>
       <c r="E10" s="26" t="n">
-        <v>112.6</v>
+        <v>300</v>
       </c>
       <c r="F10" s="27" t="n">
-        <v>449949.6</v>
+        <v>155400</v>
       </c>
       <c r="G10" s="23" t="n">
         <v>1</v>
@@ -7847,22 +7335,22 @@
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>Infraestrutura de automação</t>
+          <t>Serviço de Bota-fora - Estaca</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="D11" s="25" t="n">
-        <v>1</v>
+        <v>2242.48</v>
       </c>
       <c r="E11" s="26" t="n">
-        <v>253666.62</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="F11" s="27" t="n">
-        <v>253666.62</v>
+        <v>152892.2864</v>
       </c>
       <c r="G11" s="23" t="n">
         <v>1</v>
@@ -7879,22 +7367,22 @@
       </c>
       <c r="B12" s="24" t="inlineStr">
         <is>
-          <t>Execucao Estaca Helice Continua 040Cm</t>
+          <t>Fabricação e montagem de forma para bloco de fundação - em madeira Compensada Resinada</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>1808</v>
+        <v>2074.98</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>101.44</v>
+        <v>68.30240000000001</v>
       </c>
       <c r="F12" s="27" t="n">
-        <v>183403.52</v>
+        <v>141726.113952</v>
       </c>
       <c r="G12" s="23" t="n">
         <v>1</v>
@@ -7911,22 +7399,22 @@
       </c>
       <c r="B13" s="24" t="inlineStr">
         <is>
-          <t>Serviço de Bota-fora - Valas de Infraestrutura</t>
+          <t>Infraestrutura para carregamento de carro elétrico</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>pto</t>
         </is>
       </c>
       <c r="D13" s="25" t="n">
-        <v>3807.55</v>
+        <v>104</v>
       </c>
       <c r="E13" s="26" t="n">
-        <v>45.45</v>
+        <v>550</v>
       </c>
       <c r="F13" s="27" t="n">
-        <v>173053.1475</v>
+        <v>57200</v>
       </c>
       <c r="G13" s="23" t="n">
         <v>1</v>
@@ -7943,283 +7431,27 @@
       </c>
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>Serviço de Arrasamento Mecanizado de Estacas</t>
+          <t>Apiloamento de solo para elementos de infraestrutura</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>518</v>
+        <v>1467.69</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>300</v>
+        <v>7.27</v>
       </c>
       <c r="F14" s="27" t="n">
-        <v>155400</v>
+        <v>10670.1063</v>
       </c>
       <c r="G14" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H14" s="24" t="inlineStr">
-        <is>
-          <t>fg-scenarium</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="23" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="24" t="inlineStr">
-        <is>
-          <t>Serviço de Bota-fora - Estaca</t>
-        </is>
-      </c>
-      <c r="C15" s="23" t="inlineStr">
-        <is>
-          <t>m3</t>
-        </is>
-      </c>
-      <c r="D15" s="25" t="n">
-        <v>2242.48</v>
-      </c>
-      <c r="E15" s="26" t="n">
-        <v>68.18000000000001</v>
-      </c>
-      <c r="F15" s="27" t="n">
-        <v>152892.2864</v>
-      </c>
-      <c r="G15" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" s="24" t="inlineStr">
-        <is>
-          <t>fg-scenarium</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="23" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="24" t="inlineStr">
-        <is>
-          <t>Projeto De Fundação</t>
-        </is>
-      </c>
-      <c r="C16" s="23" t="inlineStr">
-        <is>
-          <t>vb</t>
-        </is>
-      </c>
-      <c r="D16" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="26" t="n">
-        <v>146572.7</v>
-      </c>
-      <c r="F16" s="27" t="n">
-        <v>146572.7</v>
-      </c>
-      <c r="G16" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" s="24" t="inlineStr">
-        <is>
-          <t>fg-scenarium</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="23" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="24" t="inlineStr">
-        <is>
-          <t>Fabricação e montagem de forma para bloco de fundação - em madeira Compensada Resinada</t>
-        </is>
-      </c>
-      <c r="C17" s="23" t="inlineStr">
-        <is>
-          <t>m2</t>
-        </is>
-      </c>
-      <c r="D17" s="25" t="n">
-        <v>2074.98</v>
-      </c>
-      <c r="E17" s="26" t="n">
-        <v>68.30240000000001</v>
-      </c>
-      <c r="F17" s="27" t="n">
-        <v>141726.113952</v>
-      </c>
-      <c r="G17" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" s="24" t="inlineStr">
-        <is>
-          <t>fg-scenarium</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="23" t="n">
-        <v>14</v>
-      </c>
-      <c r="B18" s="24" t="inlineStr">
-        <is>
-          <t>Infraestrutura para carregamento de carro elétrico</t>
-        </is>
-      </c>
-      <c r="C18" s="23" t="inlineStr">
-        <is>
-          <t>pto</t>
-        </is>
-      </c>
-      <c r="D18" s="25" t="n">
-        <v>104</v>
-      </c>
-      <c r="E18" s="26" t="n">
-        <v>550</v>
-      </c>
-      <c r="F18" s="27" t="n">
-        <v>57200</v>
-      </c>
-      <c r="G18" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" s="24" t="inlineStr">
-        <is>
-          <t>fg-scenarium</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="23" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="24" t="inlineStr">
-        <is>
-          <t>Ensaios de prova de carga de fundação</t>
-        </is>
-      </c>
-      <c r="C19" s="23" t="inlineStr">
-        <is>
-          <t>vb</t>
-        </is>
-      </c>
-      <c r="D19" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" s="26" t="n">
-        <v>19166.15</v>
-      </c>
-      <c r="F19" s="27" t="n">
-        <v>19166.15</v>
-      </c>
-      <c r="G19" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" s="24" t="inlineStr">
-        <is>
-          <t>fg-scenarium</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="23" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" s="24" t="inlineStr">
-        <is>
-          <t>Mobilizacao/Desmobilizacao Equipamento Fundacao - Estaca Raíz</t>
-        </is>
-      </c>
-      <c r="C20" s="23" t="inlineStr">
-        <is>
-          <t>vb</t>
-        </is>
-      </c>
-      <c r="D20" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" s="26" t="n">
-        <v>14050</v>
-      </c>
-      <c r="F20" s="27" t="n">
-        <v>14050</v>
-      </c>
-      <c r="G20" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" s="24" t="inlineStr">
-        <is>
-          <t>fg-scenarium</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="23" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" s="24" t="inlineStr">
-        <is>
-          <t>Apiloamento de solo para elementos de infraestrutura</t>
-        </is>
-      </c>
-      <c r="C21" s="23" t="inlineStr">
-        <is>
-          <t>m2</t>
-        </is>
-      </c>
-      <c r="D21" s="25" t="n">
-        <v>1467.69</v>
-      </c>
-      <c r="E21" s="26" t="n">
-        <v>7.27</v>
-      </c>
-      <c r="F21" s="27" t="n">
-        <v>10670.1063</v>
-      </c>
-      <c r="G21" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" s="24" t="inlineStr">
-        <is>
-          <t>fg-scenarium</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="23" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="24" t="inlineStr">
-        <is>
-          <t>Estudo concreto massa - bloco de fundação</t>
-        </is>
-      </c>
-      <c r="C22" s="23" t="inlineStr">
-        <is>
-          <t>vb</t>
-        </is>
-      </c>
-      <c r="D22" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" s="26" t="n">
-        <v>3625</v>
-      </c>
-      <c r="F22" s="27" t="n">
-        <v>3625</v>
-      </c>
-      <c r="G22" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" s="24" t="inlineStr">
         <is>
           <t>fg-scenarium</t>
         </is>
@@ -9595,7 +8827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -9766,22 +8998,22 @@
       </c>
       <c r="B8" s="24" t="inlineStr">
         <is>
-          <t>Projeto De Impermeabilização</t>
+          <t>Regularizacao de superficie para impermeabilizacao</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>1</v>
+        <v>2044.885</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>20609.1</v>
+        <v>6.018</v>
       </c>
       <c r="F8" s="27" t="n">
-        <v>20609.1</v>
+        <v>12306.11793</v>
       </c>
       <c r="G8" s="23" t="n">
         <v>1</v>
@@ -9798,7 +9030,7 @@
       </c>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>Regularizacao de superficie para impermeabilizacao</t>
+          <t>Impermeabilização De Superfície Com Argamassa Polimérica, 3 Demãos</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
@@ -9807,13 +9039,13 @@
         </is>
       </c>
       <c r="D9" s="25" t="n">
-        <v>2044.885</v>
+        <v>123.69</v>
       </c>
       <c r="E9" s="26" t="n">
-        <v>6.018</v>
+        <v>39.2187</v>
       </c>
       <c r="F9" s="27" t="n">
-        <v>12306.11793</v>
+        <v>4850.961002999999</v>
       </c>
       <c r="G9" s="23" t="n">
         <v>1</v>
@@ -9830,7 +9062,7 @@
       </c>
       <c r="B10" s="24" t="inlineStr">
         <is>
-          <t>Impermeabilização De Superfície Com Argamassa Polimérica, 3 Demãos</t>
+          <t>Mão de obra impermeabilização de argamassa polimérica</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
@@ -9842,47 +9074,15 @@
         <v>123.69</v>
       </c>
       <c r="E10" s="26" t="n">
-        <v>39.2187</v>
+        <v>25</v>
       </c>
       <c r="F10" s="27" t="n">
-        <v>4850.961002999999</v>
+        <v>3092.25</v>
       </c>
       <c r="G10" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H10" s="24" t="inlineStr">
-        <is>
-          <t>fg-scenarium</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="24" t="inlineStr">
-        <is>
-          <t>Mão de obra impermeabilização de argamassa polimérica</t>
-        </is>
-      </c>
-      <c r="C11" s="23" t="inlineStr">
-        <is>
-          <t>m2</t>
-        </is>
-      </c>
-      <c r="D11" s="25" t="n">
-        <v>123.69</v>
-      </c>
-      <c r="E11" s="26" t="n">
-        <v>25</v>
-      </c>
-      <c r="F11" s="27" t="n">
-        <v>3092.25</v>
-      </c>
-      <c r="G11" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="24" t="inlineStr">
         <is>
           <t>fg-scenarium</t>
         </is>
@@ -10011,7 +9211,7 @@
       </c>
       <c r="B6" s="24" t="inlineStr">
         <is>
-          <t>Sistema completo de antena  de televisão para 1240 pontos, contendo amplificadores de potência, distribuidores e antenas para todos os canais de televisão e rádios FM</t>
+          <t>Quadro de distribuição para telecomunicações (10U/10") , dimensões conforme padrão Beco Castelo</t>
         </is>
       </c>
       <c r="C6" s="23" t="inlineStr">
@@ -10020,13 +9220,13 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>1</v>
+        <v>142</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>851880</v>
+        <v>2500</v>
       </c>
       <c r="F6" s="27" t="n">
-        <v>851880</v>
+        <v>355000</v>
       </c>
       <c r="G6" s="23" t="n">
         <v>1</v>
@@ -10043,22 +9243,22 @@
       </c>
       <c r="B7" s="24" t="inlineStr">
         <is>
-          <t>Fios e Cabos Elétricos</t>
+          <t>Mão de obra instalações preventivas</t>
         </is>
       </c>
       <c r="C7" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="D7" s="25" t="n">
-        <v>1</v>
+        <v>42277.77</v>
       </c>
       <c r="E7" s="26" t="n">
-        <v>602135.46</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F7" s="27" t="n">
-        <v>602135.46</v>
+        <v>346677.7139999999</v>
       </c>
       <c r="G7" s="23" t="n">
         <v>1</v>
@@ -10075,29 +9275,29 @@
       </c>
       <c r="B8" s="24" t="inlineStr">
         <is>
-          <t>Subestação</t>
+          <t>ELETRODUTO DE PVC RÍGIDO, TIPO ROSCA, Ø ¾”</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>1</v>
+        <v>37500</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>528496.85</v>
+        <v>8.299999999999999</v>
       </c>
       <c r="F8" s="27" t="n">
-        <v>528496.85</v>
+        <v>311249.9999999999</v>
       </c>
       <c r="G8" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H8" s="24" t="inlineStr">
         <is>
-          <t>fg-scenarium</t>
+          <t>beco-castelo-chateau-de-versailes</t>
         </is>
       </c>
     </row>
@@ -10107,22 +9307,22 @@
       </c>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>Quadro de distribuição para telecomunicações (10U/10") , dimensões conforme padrão Beco Castelo</t>
+          <t>Arame guia galvanizado, seção 14 AWG, para ser passado em todas as tubulações telefônicas/antena coletiva/ porteiro eletrónico/ lógica/ sonorização</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D9" s="25" t="n">
-        <v>142</v>
+        <v>48000</v>
       </c>
       <c r="E9" s="26" t="n">
-        <v>2500</v>
+        <v>4</v>
       </c>
       <c r="F9" s="27" t="n">
-        <v>355000</v>
+        <v>192000</v>
       </c>
       <c r="G9" s="23" t="n">
         <v>1</v>
@@ -10139,29 +9339,29 @@
       </c>
       <c r="B10" s="24" t="inlineStr">
         <is>
-          <t>Mão de obra instalações preventivas</t>
+          <t>QUADRO GERAL E OU DE DISTRIBUIÇÃO METÁLICO PARA SUPERVISÃO E AUTOMAÇÃO (IP-54), COM PORTA E FECHADURA, Dimensão conforme padrão da construtora para as áreas comuns</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>un</t>
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>42277.77</v>
+        <v>84</v>
       </c>
       <c r="E10" s="26" t="n">
-        <v>8.199999999999999</v>
+        <v>2000</v>
       </c>
       <c r="F10" s="27" t="n">
-        <v>346677.7139999999</v>
+        <v>168000</v>
       </c>
       <c r="G10" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H10" s="24" t="inlineStr">
         <is>
-          <t>fg-scenarium</t>
+          <t>beco-castelo-chateau-de-versailes</t>
         </is>
       </c>
     </row>
@@ -10171,7 +9371,7 @@
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>ELETRODUTO DE PVC RÍGIDO, TIPO ROSCA, Ø ¾”</t>
+          <t>Cabo de logica UTP-4P tipo par trançado - categoria 6 gigalan AZ Cat.6 CMX</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
@@ -10180,13 +9380,13 @@
         </is>
       </c>
       <c r="D11" s="25" t="n">
-        <v>37500</v>
+        <v>43615</v>
       </c>
       <c r="E11" s="26" t="n">
-        <v>8.299999999999999</v>
+        <v>3.56</v>
       </c>
       <c r="F11" s="27" t="n">
-        <v>311249.9999999999</v>
+        <v>155269.4</v>
       </c>
       <c r="G11" s="23" t="n">
         <v>1</v>
@@ -10203,29 +9403,29 @@
       </c>
       <c r="B12" s="24" t="inlineStr">
         <is>
-          <t>Projeto Elétrico/Comunicação/Telefonia/Luminotécnico</t>
+          <t>Cabo interno òptico - Cabo Fiber-Lan 50/125x2 Fibras Furukawa</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>1</v>
+        <v>43615</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>299127.96</v>
+        <v>3.56</v>
       </c>
       <c r="F12" s="27" t="n">
-        <v>299127.96</v>
+        <v>155269.4</v>
       </c>
       <c r="G12" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H12" s="24" t="inlineStr">
         <is>
-          <t>fg-scenarium</t>
+          <t>beco-castelo-chateau-de-versailes</t>
         </is>
       </c>
     </row>
@@ -10235,22 +9435,22 @@
       </c>
       <c r="B13" s="24" t="inlineStr">
         <is>
-          <t>Instalações Provisórias - Elétricas, comunicação, Dados e Hidrossanitários</t>
+          <t>Manutenção Elétrica Provisória</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>mes</t>
         </is>
       </c>
       <c r="D13" s="25" t="n">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="E13" s="26" t="n">
-        <v>268829.96</v>
+        <v>3052.11</v>
       </c>
       <c r="F13" s="27" t="n">
-        <v>268829.96</v>
+        <v>149553.39</v>
       </c>
       <c r="G13" s="23" t="n">
         <v>1</v>
@@ -10267,29 +9467,29 @@
       </c>
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>Suportes, módulos e acabamentos elétricos</t>
+          <t>01 leitor Biometria</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>un</t>
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>1</v>
+        <v>284</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>243709.12</v>
+        <v>484.5</v>
       </c>
       <c r="F14" s="27" t="n">
-        <v>243709.12</v>
+        <v>137598</v>
       </c>
       <c r="G14" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H14" s="24" t="inlineStr">
         <is>
-          <t>fg-scenarium</t>
+          <t>beco-castelo-chateau-de-versailes</t>
         </is>
       </c>
     </row>
@@ -10299,22 +9499,22 @@
       </c>
       <c r="B15" s="24" t="inlineStr">
         <is>
-          <t>Sistema SPDA</t>
+          <t>Manutenção Hidrossanitário Provisória</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>mes</t>
         </is>
       </c>
       <c r="D15" s="25" t="n">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="E15" s="26" t="n">
-        <v>202069.84</v>
+        <v>2671.19</v>
       </c>
       <c r="F15" s="27" t="n">
-        <v>202069.84</v>
+        <v>130888.31</v>
       </c>
       <c r="G15" s="23" t="n">
         <v>1</v>
@@ -10331,7 +9531,7 @@
       </c>
       <c r="B16" s="24" t="inlineStr">
         <is>
-          <t>Arame guia galvanizado, seção 14 AWG, para ser passado em todas as tubulações telefônicas/antena coletiva/ porteiro eletrónico/ lógica/ sonorização</t>
+          <t>ELETRODUTO DE PVC RÍGIDO, TIPO ROSCA, Ø 1”</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
@@ -10340,13 +9540,13 @@
         </is>
       </c>
       <c r="D16" s="25" t="n">
-        <v>48000</v>
+        <v>10800</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>4</v>
+        <v>9.273333333333333</v>
       </c>
       <c r="F16" s="27" t="n">
-        <v>192000</v>
+        <v>100152</v>
       </c>
       <c r="G16" s="23" t="n">
         <v>1</v>
@@ -10363,7 +9563,7 @@
       </c>
       <c r="B17" s="24" t="inlineStr">
         <is>
-          <t>QUADRO GERAL E OU DE DISTRIBUIÇÃO METÁLICO PARA SUPERVISÃO E AUTOMAÇÃO (IP-54), COM PORTA E FECHADURA, Dimensão conforme padrão da construtora para as áreas comuns</t>
+          <t>01 interrupor de comando da persiana</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -10372,13 +9572,13 @@
         </is>
       </c>
       <c r="D17" s="25" t="n">
-        <v>84</v>
+        <v>553</v>
       </c>
       <c r="E17" s="26" t="n">
-        <v>2000</v>
+        <v>108.96</v>
       </c>
       <c r="F17" s="27" t="n">
-        <v>168000</v>
+        <v>60254.88</v>
       </c>
       <c r="G17" s="23" t="n">
         <v>1</v>
@@ -10395,29 +9595,29 @@
       </c>
       <c r="B18" s="24" t="inlineStr">
         <is>
-          <t>Sistema de bombas e pressurização hidráulica</t>
+          <t>Arandela blindada em alumínio pintado, modelo a ser definido, com  uma  lâmpada 3W-LED , para os depósitos</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>un</t>
         </is>
       </c>
       <c r="D18" s="25" t="n">
-        <v>1</v>
+        <v>142</v>
       </c>
       <c r="E18" s="26" t="n">
-        <v>159795.86</v>
+        <v>383.05</v>
       </c>
       <c r="F18" s="27" t="n">
-        <v>159795.86</v>
+        <v>54393.1</v>
       </c>
       <c r="G18" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H18" s="24" t="inlineStr">
         <is>
-          <t>fg-scenarium</t>
+          <t>beco-castelo-chateau-de-versailes</t>
         </is>
       </c>
     </row>
@@ -10427,22 +9627,22 @@
       </c>
       <c r="B19" s="24" t="inlineStr">
         <is>
-          <t>Cabo de logica UTP-4P tipo par trançado - categoria 6 gigalan AZ Cat.6 CMX</t>
+          <t>Placa com 2 tomadas para conector RJ-45</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>un</t>
         </is>
       </c>
       <c r="D19" s="25" t="n">
-        <v>43615</v>
+        <v>1222</v>
       </c>
       <c r="E19" s="26" t="n">
-        <v>3.56</v>
+        <v>32.97</v>
       </c>
       <c r="F19" s="27" t="n">
-        <v>155269.4</v>
+        <v>40289.34</v>
       </c>
       <c r="G19" s="23" t="n">
         <v>1</v>
@@ -10459,7 +9659,7 @@
       </c>
       <c r="B20" s="24" t="inlineStr">
         <is>
-          <t>Cabo interno òptico - Cabo Fiber-Lan 50/125x2 Fibras Furukawa</t>
+          <t>CABOS  DO TIPO EPROTENAX  1000 V (90o) 185mm²</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -10468,13 +9668,13 @@
         </is>
       </c>
       <c r="D20" s="25" t="n">
-        <v>43615</v>
+        <v>230</v>
       </c>
       <c r="E20" s="26" t="n">
-        <v>3.56</v>
+        <v>168.98</v>
       </c>
       <c r="F20" s="27" t="n">
-        <v>155269.4</v>
+        <v>38865.39999999999</v>
       </c>
       <c r="G20" s="23" t="n">
         <v>1</v>
@@ -10491,29 +9691,29 @@
       </c>
       <c r="B21" s="24" t="inlineStr">
         <is>
-          <t>Manutenção Elétrica Provisória</t>
+          <t>01 pulsador ou teclado de comando da iluminação</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
         <is>
-          <t>mes</t>
+          <t>un</t>
         </is>
       </c>
       <c r="D21" s="25" t="n">
-        <v>49</v>
+        <v>2516</v>
       </c>
       <c r="E21" s="26" t="n">
-        <v>3052.11</v>
+        <v>14.21</v>
       </c>
       <c r="F21" s="27" t="n">
-        <v>149553.39</v>
+        <v>35752.36</v>
       </c>
       <c r="G21" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H21" s="24" t="inlineStr">
         <is>
-          <t>fg-scenarium</t>
+          <t>beco-castelo-chateau-de-versailes</t>
         </is>
       </c>
     </row>
@@ -10523,22 +9723,22 @@
       </c>
       <c r="B22" s="24" t="inlineStr">
         <is>
-          <t>01 leitor Biometria</t>
+          <t>ELETRODUTO DE PVC RÍGIDO, TIPO ROSCA, Ø 1 ¼”</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D22" s="25" t="n">
-        <v>284</v>
+        <v>2034</v>
       </c>
       <c r="E22" s="26" t="n">
-        <v>484.5</v>
+        <v>16.63333333333333</v>
       </c>
       <c r="F22" s="27" t="n">
-        <v>137598</v>
+        <v>33832.2</v>
       </c>
       <c r="G22" s="23" t="n">
         <v>1</v>
@@ -10555,29 +9755,29 @@
       </c>
       <c r="B23" s="24" t="inlineStr">
         <is>
-          <t>Manutenção Hidrossanitário Provisória</t>
+          <t>CABOS DO TIPO ANTI-CHAMA, ISOLAMENTO PARA 750 V (70o) 2,5mm²</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
         <is>
-          <t>mes</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D23" s="25" t="n">
-        <v>49</v>
+        <v>3200</v>
       </c>
       <c r="E23" s="26" t="n">
-        <v>2671.19</v>
+        <v>6.12505</v>
       </c>
       <c r="F23" s="27" t="n">
-        <v>130888.31</v>
+        <v>19600.16</v>
       </c>
       <c r="G23" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H23" s="24" t="inlineStr">
         <is>
-          <t>fg-scenarium</t>
+          <t>beco-castelo-chateau-de-versailes</t>
         </is>
       </c>
     </row>
@@ -10587,29 +9787,29 @@
       </c>
       <c r="B24" s="24" t="inlineStr">
         <is>
-          <t>Projeto Hidrossanitário/Drenagem/Pluvial</t>
+          <t>20 x 20 x 10 cm (de embutir) - Caixa de passagem</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>un</t>
         </is>
       </c>
       <c r="D24" s="25" t="n">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="E24" s="26" t="n">
-        <v>122902.57</v>
+        <v>333.3333333333333</v>
       </c>
       <c r="F24" s="27" t="n">
-        <v>122902.57</v>
+        <v>30000</v>
       </c>
       <c r="G24" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H24" s="24" t="inlineStr">
         <is>
-          <t>fg-scenarium</t>
+          <t>beco-castelo-chateau-de-versailes</t>
         </is>
       </c>
     </row>
@@ -10619,22 +9819,22 @@
       </c>
       <c r="B25" s="24" t="inlineStr">
         <is>
-          <t>ELETRODUTO DE PVC RÍGIDO, TIPO ROSCA, Ø 1”</t>
+          <t>02 tomadas 2P+T (10A)</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>un</t>
         </is>
       </c>
       <c r="D25" s="25" t="n">
-        <v>10800</v>
+        <v>2506</v>
       </c>
       <c r="E25" s="26" t="n">
-        <v>9.273333333333333</v>
+        <v>11.51</v>
       </c>
       <c r="F25" s="27" t="n">
-        <v>100152</v>
+        <v>28844.06</v>
       </c>
       <c r="G25" s="23" t="n">
         <v>1</v>
@@ -10651,7 +9851,7 @@
       </c>
       <c r="B26" s="24" t="inlineStr">
         <is>
-          <t>01 interrupor de comando da persiana</t>
+          <t>Caixa de PVC rígido, cor amarela com orelhas metálicas, fabricação  Tigre , Wetzel ou equivalente, dimensões 2”x 4”</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
@@ -10660,13 +9860,13 @@
         </is>
       </c>
       <c r="D26" s="25" t="n">
-        <v>553</v>
+        <v>10703</v>
       </c>
       <c r="E26" s="26" t="n">
-        <v>108.96</v>
+        <v>2.68</v>
       </c>
       <c r="F26" s="27" t="n">
-        <v>60254.88</v>
+        <v>28684.04</v>
       </c>
       <c r="G26" s="23" t="n">
         <v>1</v>
@@ -10683,29 +9883,29 @@
       </c>
       <c r="B27" s="24" t="inlineStr">
         <is>
-          <t>Projeto Preventivo (Ppci - Plano De Prevenção E Proteção Contra Incêndios) E Gás</t>
+          <t>CABOS  DO TIPO EPROTENAX  1000 V (90o) 35mm²</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D27" s="25" t="n">
-        <v>1</v>
+        <v>840</v>
       </c>
       <c r="E27" s="26" t="n">
-        <v>58264.92</v>
+        <v>33.52</v>
       </c>
       <c r="F27" s="27" t="n">
-        <v>58264.92</v>
+        <v>28156.8</v>
       </c>
       <c r="G27" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H27" s="24" t="inlineStr">
         <is>
-          <t>fg-scenarium</t>
+          <t>beco-castelo-chateau-de-versailes</t>
         </is>
       </c>
     </row>
@@ -10715,7 +9915,7 @@
       </c>
       <c r="B28" s="24" t="inlineStr">
         <is>
-          <t>Arandela blindada em alumínio pintado, modelo a ser definido, com  uma  lâmpada 3W-LED , para os depósitos</t>
+          <t>01 tomada 2P+T (20A)  do tipo AQUATIC</t>
         </is>
       </c>
       <c r="C28" s="23" t="inlineStr">
@@ -10724,13 +9924,13 @@
         </is>
       </c>
       <c r="D28" s="25" t="n">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="E28" s="26" t="n">
-        <v>383.05</v>
+        <v>168.1</v>
       </c>
       <c r="F28" s="27" t="n">
-        <v>54393.1</v>
+        <v>23197.8</v>
       </c>
       <c r="G28" s="23" t="n">
         <v>1</v>
@@ -10747,7 +9947,7 @@
       </c>
       <c r="B29" s="24" t="inlineStr">
         <is>
-          <t>Placa com 2 tomadas para conector RJ-45</t>
+          <t>01 tomada 2P+T (20A)</t>
         </is>
       </c>
       <c r="C29" s="23" t="inlineStr">
@@ -10756,13 +9956,13 @@
         </is>
       </c>
       <c r="D29" s="25" t="n">
-        <v>1222</v>
+        <v>1773</v>
       </c>
       <c r="E29" s="26" t="n">
-        <v>32.97</v>
+        <v>12.4</v>
       </c>
       <c r="F29" s="27" t="n">
-        <v>40289.34</v>
+        <v>21985.2</v>
       </c>
       <c r="G29" s="23" t="n">
         <v>1</v>
@@ -10779,22 +9979,22 @@
       </c>
       <c r="B30" s="24" t="inlineStr">
         <is>
-          <t>CABOS  DO TIPO EPROTENAX  1000 V (90o) 185mm²</t>
+          <t>Arandela blindada, uso externo, com lâmpada 10W-LED (3000k), modelo a ser definido</t>
         </is>
       </c>
       <c r="C30" s="23" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>un</t>
         </is>
       </c>
       <c r="D30" s="25" t="n">
-        <v>230</v>
+        <v>69</v>
       </c>
       <c r="E30" s="26" t="n">
-        <v>168.98</v>
+        <v>249.99</v>
       </c>
       <c r="F30" s="27" t="n">
-        <v>38865.39999999999</v>
+        <v>17249.31</v>
       </c>
       <c r="G30" s="23" t="n">
         <v>1</v>
@@ -10811,7 +10011,7 @@
       </c>
       <c r="B31" s="24" t="inlineStr">
         <is>
-          <t>01 pulsador ou teclado de comando da iluminação</t>
+          <t>Luminária de sobrepor com lâmpada de 12W - LED, para as áreas comuns, modelo a ser definido.</t>
         </is>
       </c>
       <c r="C31" s="23" t="inlineStr">
@@ -10820,13 +10020,13 @@
         </is>
       </c>
       <c r="D31" s="25" t="n">
-        <v>2516</v>
+        <v>460</v>
       </c>
       <c r="E31" s="26" t="n">
-        <v>14.21</v>
+        <v>36.71</v>
       </c>
       <c r="F31" s="27" t="n">
-        <v>35752.36</v>
+        <v>16886.6</v>
       </c>
       <c r="G31" s="23" t="n">
         <v>1</v>
@@ -10843,29 +10043,29 @@
       </c>
       <c r="B32" s="24" t="inlineStr">
         <is>
-          <t>ELETRODUTO DE PVC RÍGIDO, TIPO ROSCA, Ø 1 ¼”</t>
+          <t>Revestimento em Ladrilho Hidráulico Cimentício</t>
         </is>
       </c>
       <c r="C32" s="23" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="D32" s="25" t="n">
-        <v>2034</v>
+        <v>323.36</v>
       </c>
       <c r="E32" s="26" t="n">
-        <v>16.63333333333333</v>
+        <v>51.9092</v>
       </c>
       <c r="F32" s="27" t="n">
-        <v>33832.2</v>
+        <v>16785.358912</v>
       </c>
       <c r="G32" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H32" s="24" t="inlineStr">
         <is>
-          <t>beco-castelo-chateau-de-versailes</t>
+          <t>fg-scenarium</t>
         </is>
       </c>
     </row>
@@ -10875,22 +10075,22 @@
       </c>
       <c r="B33" s="24" t="inlineStr">
         <is>
-          <t>CABOS DO TIPO ANTI-CHAMA, ISOLAMENTO PARA 750 V (70o) 2,5mm²</t>
+          <t>Sensor de aproximação de teto, com raio de atuação de 360º, 10A, 220V, fabricação Pial-Legrand, Siemens, Finder ou equivalente</t>
         </is>
       </c>
       <c r="C33" s="23" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>un</t>
         </is>
       </c>
       <c r="D33" s="25" t="n">
-        <v>3200</v>
+        <v>249</v>
       </c>
       <c r="E33" s="26" t="n">
-        <v>6.12505</v>
+        <v>64.7</v>
       </c>
       <c r="F33" s="27" t="n">
-        <v>19600.16</v>
+        <v>16110.3</v>
       </c>
       <c r="G33" s="23" t="n">
         <v>1</v>
@@ -10907,7 +10107,7 @@
       </c>
       <c r="B34" s="24" t="inlineStr">
         <is>
-          <t>20 x 20 x 10 cm (de embutir) - Caixa de passagem</t>
+          <t>02 tomadas 2P+T (20A)</t>
         </is>
       </c>
       <c r="C34" s="23" t="inlineStr">
@@ -10916,13 +10116,13 @@
         </is>
       </c>
       <c r="D34" s="25" t="n">
-        <v>90</v>
+        <v>478</v>
       </c>
       <c r="E34" s="26" t="n">
-        <v>333.3333333333333</v>
+        <v>29.61</v>
       </c>
       <c r="F34" s="27" t="n">
-        <v>30000</v>
+        <v>14153.58</v>
       </c>
       <c r="G34" s="23" t="n">
         <v>1</v>
@@ -11024,22 +10224,22 @@
       </c>
       <c r="B5" s="24" t="inlineStr">
         <is>
-          <t>Equipamentos e fornecimento de piscinas IGUI</t>
+          <t>Locação Elevador Cremalheira</t>
         </is>
       </c>
       <c r="C5" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>mes</t>
         </is>
       </c>
       <c r="D5" s="25" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="E5" s="26" t="n">
-        <v>5300359.1</v>
+        <v>19200</v>
       </c>
       <c r="F5" s="27" t="n">
-        <v>5300359.1</v>
+        <v>537600</v>
       </c>
       <c r="G5" s="23" t="n">
         <v>1</v>
@@ -11056,29 +10256,29 @@
       </c>
       <c r="B6" s="24" t="inlineStr">
         <is>
-          <t>Elevadores</t>
+          <t>28.04</t>
         </is>
       </c>
       <c r="C6" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>1737485.29</v>
+        <v>35050</v>
       </c>
       <c r="F6" s="27" t="n">
-        <v>1737485.29</v>
+        <v>43812.5</v>
       </c>
       <c r="G6" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H6" s="24" t="inlineStr">
         <is>
-          <t>fg-scenarium</t>
+          <t>beco-castelo-chateau-de-versailes</t>
         </is>
       </c>
     </row>
@@ -11088,22 +10288,22 @@
       </c>
       <c r="B7" s="24" t="inlineStr">
         <is>
-          <t>Locação Elevador Cremalheira</t>
+          <t>Montagem E Desmontagem Elevador Cremalheira</t>
         </is>
       </c>
       <c r="C7" s="23" t="inlineStr">
         <is>
-          <t>mes</t>
+          <t>un</t>
         </is>
       </c>
       <c r="D7" s="25" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="E7" s="26" t="n">
-        <v>19200</v>
+        <v>16300</v>
       </c>
       <c r="F7" s="27" t="n">
-        <v>537600</v>
+        <v>32600</v>
       </c>
       <c r="G7" s="23" t="n">
         <v>1</v>
@@ -11120,29 +10320,29 @@
       </c>
       <c r="B8" s="24" t="inlineStr">
         <is>
-          <t>Automação iluminação de emergência</t>
+          <t>24.21</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>31.473000000000003</t>
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>487214.06</v>
+        <v>31473</v>
       </c>
       <c r="F8" s="27" t="n">
-        <v>487214.06</v>
+        <v>40914.90000000001</v>
       </c>
       <c r="G8" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H8" s="24" t="inlineStr">
         <is>
-          <t>fg-scenarium</t>
+          <t>beco-castelo-chateau-de-versailes</t>
         </is>
       </c>
     </row>
@@ -11152,29 +10352,29 @@
       </c>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>Sistema Gerador</t>
+          <t>19.82</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>25.766000000000002</t>
         </is>
       </c>
       <c r="D9" s="25" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="E9" s="26" t="n">
-        <v>249995</v>
+        <v>25766</v>
       </c>
       <c r="F9" s="27" t="n">
-        <v>249995</v>
+        <v>33495.8</v>
       </c>
       <c r="G9" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H9" s="24" t="inlineStr">
         <is>
-          <t>fg-scenarium</t>
+          <t>beco-castelo-chateau-de-versailes</t>
         </is>
       </c>
     </row>
@@ -11184,29 +10384,29 @@
       </c>
       <c r="B10" s="24" t="inlineStr">
         <is>
-          <t>Equipamentos e fornecimento de piscinas</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E10" s="26" t="n">
-        <v>232119.75</v>
+        <v>5400</v>
       </c>
       <c r="F10" s="27" t="n">
-        <v>232119.75</v>
+        <v>2700</v>
       </c>
       <c r="G10" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H10" s="24" t="inlineStr">
         <is>
-          <t>fg-scenarium</t>
+          <t>beco-castelo-chateau-de-versailes</t>
         </is>
       </c>
     </row>
@@ -11216,22 +10416,22 @@
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>Gerador Autônomo De Energia</t>
+          <t>Mao De Obra Para Pintura de Poço do Elevador, 2 Demaos</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="D11" s="25" t="n">
-        <v>1</v>
+        <v>294.945</v>
       </c>
       <c r="E11" s="26" t="n">
-        <v>196503.54</v>
+        <v>16</v>
       </c>
       <c r="F11" s="27" t="n">
-        <v>196503.54</v>
+        <v>4719.12</v>
       </c>
       <c r="G11" s="23" t="n">
         <v>1</v>
@@ -11248,29 +10448,29 @@
       </c>
       <c r="B12" s="24" t="inlineStr">
         <is>
-          <t>Instalação de CFTV</t>
+          <t>GERADOR DE COLORO BZ -30</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>un</t>
         </is>
       </c>
       <c r="D12" s="25" t="n">
         <v>1</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>146428.7</v>
+        <v>3656.75</v>
       </c>
       <c r="F12" s="27" t="n">
-        <v>146428.7</v>
+        <v>3656.75</v>
       </c>
       <c r="G12" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H12" s="24" t="inlineStr">
         <is>
-          <t>fg-scenarium</t>
+          <t>beco-castelo-chateau-de-versailes</t>
         </is>
       </c>
     </row>
@@ -11280,29 +10480,29 @@
       </c>
       <c r="B13" s="24" t="inlineStr">
         <is>
-          <t>Sistema de detecção e alarme</t>
+          <t>11.16</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>3.3479999999999683</t>
         </is>
       </c>
       <c r="D13" s="25" t="n">
-        <v>1</v>
+        <v>0.2999999999999972</v>
       </c>
       <c r="E13" s="26" t="n">
-        <v>118377.76</v>
+        <v>3347.999999999968</v>
       </c>
       <c r="F13" s="27" t="n">
-        <v>118377.76</v>
+        <v>1004.399999999981</v>
       </c>
       <c r="G13" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H13" s="24" t="inlineStr">
         <is>
-          <t>fg-scenarium</t>
+          <t>beco-castelo-chateau-de-versailes</t>
         </is>
       </c>
     </row>
@@ -11312,29 +10512,29 @@
       </c>
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>Projeto De Piscina</t>
+          <t>GERADOR DE COLORO BZ -20</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>un</t>
         </is>
       </c>
       <c r="D14" s="25" t="n">
         <v>1</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>58125.4</v>
+        <v>3296.12</v>
       </c>
       <c r="F14" s="27" t="n">
-        <v>58125.4</v>
+        <v>3296.12</v>
       </c>
       <c r="G14" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H14" s="24" t="inlineStr">
         <is>
-          <t>fg-scenarium</t>
+          <t>beco-castelo-chateau-de-versailes</t>
         </is>
       </c>
     </row>
@@ -11344,22 +10544,22 @@
       </c>
       <c r="B15" s="24" t="inlineStr">
         <is>
-          <t>28.04</t>
+          <t>TAMPA ARTICULADA GDA 110X110cm CÓDIGO 3140</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>un</t>
         </is>
       </c>
       <c r="D15" s="25" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="E15" s="26" t="n">
-        <v>35050</v>
+        <v>3200</v>
       </c>
       <c r="F15" s="27" t="n">
-        <v>43812.5</v>
+        <v>3200</v>
       </c>
       <c r="G15" s="23" t="n">
         <v>1</v>
@@ -11376,7 +10576,7 @@
       </c>
       <c r="B16" s="24" t="inlineStr">
         <is>
-          <t>Montagem E Desmontagem Elevador Cremalheira</t>
+          <t>Mobilização E Desmobilização Elevador Cremalheira</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
@@ -11388,10 +10588,10 @@
         <v>2</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>16300</v>
+        <v>1328</v>
       </c>
       <c r="F16" s="27" t="n">
-        <v>32600</v>
+        <v>2656</v>
       </c>
       <c r="G16" s="23" t="n">
         <v>1</v>
@@ -11408,22 +10608,22 @@
       </c>
       <c r="B17" s="24" t="inlineStr">
         <is>
-          <t>24.21</t>
+          <t>13.28</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
         <is>
-          <t>31.473000000000003</t>
+          <t>2.6559999999999993</t>
         </is>
       </c>
       <c r="D17" s="25" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="E17" s="26" t="n">
-        <v>31473</v>
+        <v>2655.999999999999</v>
       </c>
       <c r="F17" s="27" t="n">
-        <v>40914.90000000001</v>
+        <v>531.1999999999997</v>
       </c>
       <c r="G17" s="23" t="n">
         <v>1</v>
@@ -11440,22 +10640,22 @@
       </c>
       <c r="B18" s="24" t="inlineStr">
         <is>
-          <t>19.82</t>
+          <t>TAMPA GDA REBAIXADA C/ GRELHA 80X80cm CÓDIGO 3078</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
         <is>
-          <t>25.766000000000002</t>
+          <t>un</t>
         </is>
       </c>
       <c r="D18" s="25" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="E18" s="26" t="n">
-        <v>25766</v>
+        <v>1850</v>
       </c>
       <c r="F18" s="27" t="n">
-        <v>33495.8</v>
+        <v>1850</v>
       </c>
       <c r="G18" s="23" t="n">
         <v>1</v>
@@ -11472,29 +10672,30 @@
       </c>
       <c r="B19" s="24" t="inlineStr">
         <is>
-          <t>Projeto De Automação</t>
+          <t>Bomba BM-33 1/3 cv p/ piscinas de até 40 mil litros
+SODAMAR</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>un</t>
         </is>
       </c>
       <c r="D19" s="25" t="n">
         <v>1</v>
       </c>
       <c r="E19" s="26" t="n">
-        <v>13564.85</v>
+        <v>1416</v>
       </c>
       <c r="F19" s="27" t="n">
-        <v>13564.85</v>
+        <v>1416</v>
       </c>
       <c r="G19" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H19" s="24" t="inlineStr">
         <is>
-          <t>fg-scenarium</t>
+          <t>beco-castelo-chateau-de-versailes</t>
         </is>
       </c>
     </row>
@@ -11504,22 +10705,23 @@
       </c>
       <c r="B20" s="24" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>Bomba 1/4cv BM-25 p/ piscinas de até 28 mil litro
+SODAMAR</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>un</t>
         </is>
       </c>
       <c r="D20" s="25" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E20" s="26" t="n">
-        <v>5400</v>
+        <v>1317</v>
       </c>
       <c r="F20" s="27" t="n">
-        <v>2700</v>
+        <v>1317</v>
       </c>
       <c r="G20" s="23" t="n">
         <v>1</v>
@@ -11536,29 +10738,30 @@
       </c>
       <c r="B21" s="24" t="inlineStr">
         <is>
-          <t>Mao De Obra Para Pintura de Poço do Elevador, 2 Demaos</t>
+          <t>Bomba 1/4 cv BM-25 p/ piscinas de até 28 mil litros
+SODAMAR</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>un</t>
         </is>
       </c>
       <c r="D21" s="25" t="n">
-        <v>294.945</v>
+        <v>1</v>
       </c>
       <c r="E21" s="26" t="n">
-        <v>16</v>
+        <v>1055</v>
       </c>
       <c r="F21" s="27" t="n">
-        <v>4719.12</v>
+        <v>1055</v>
       </c>
       <c r="G21" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H21" s="24" t="inlineStr">
         <is>
-          <t>fg-scenarium</t>
+          <t>beco-castelo-chateau-de-versailes</t>
         </is>
       </c>
     </row>
@@ -11568,7 +10771,8 @@
       </c>
       <c r="B22" s="24" t="inlineStr">
         <is>
-          <t>GERADOR DE COLORO BZ -30</t>
+          <t>Filtro para piscina FM-36 p/ até 40 mil litros
+SODAMAR</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -11580,10 +10784,10 @@
         <v>1</v>
       </c>
       <c r="E22" s="26" t="n">
-        <v>3656.75</v>
+        <v>978</v>
       </c>
       <c r="F22" s="27" t="n">
-        <v>3656.75</v>
+        <v>978</v>
       </c>
       <c r="G22" s="23" t="n">
         <v>1</v>
@@ -11600,22 +10804,23 @@
       </c>
       <c r="B23" s="24" t="inlineStr">
         <is>
-          <t>11.16</t>
+          <t>Filtro para piscina FM-30 p/ até 28 mil litros
+SODAMAR</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
         <is>
-          <t>3.3479999999999683</t>
+          <t>un</t>
         </is>
       </c>
       <c r="D23" s="25" t="n">
-        <v>0.2999999999999972</v>
+        <v>1</v>
       </c>
       <c r="E23" s="26" t="n">
-        <v>3347.999999999968</v>
+        <v>900</v>
       </c>
       <c r="F23" s="27" t="n">
-        <v>1004.399999999981</v>
+        <v>900</v>
       </c>
       <c r="G23" s="23" t="n">
         <v>1</v>
@@ -11632,29 +10837,29 @@
       </c>
       <c r="B24" s="24" t="inlineStr">
         <is>
-          <t>GERADOR DE COLORO BZ -20</t>
+          <t>Tela  Elevador em Aço Galvanizado</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="D24" s="25" t="n">
-        <v>1</v>
+        <v>55.14</v>
       </c>
       <c r="E24" s="26" t="n">
-        <v>3296.12</v>
+        <v>16.18</v>
       </c>
       <c r="F24" s="27" t="n">
-        <v>3296.12</v>
+        <v>892.1652</v>
       </c>
       <c r="G24" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H24" s="24" t="inlineStr">
         <is>
-          <t>beco-castelo-chateau-de-versailes</t>
+          <t>fg-scenarium</t>
         </is>
       </c>
     </row>
@@ -11664,7 +10869,7 @@
       </c>
       <c r="B25" s="24" t="inlineStr">
         <is>
-          <t>TAMPA ARTICULADA GDA 110X110cm CÓDIGO 3140</t>
+          <t>COADEIRA COMPACTA CRISTAL LED EM ABS C/ ACABAMENTO FRENTE EM INOX</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr">
@@ -11676,10 +10881,10 @@
         <v>1</v>
       </c>
       <c r="E25" s="26" t="n">
-        <v>3200</v>
+        <v>889</v>
       </c>
       <c r="F25" s="27" t="n">
-        <v>3200</v>
+        <v>889</v>
       </c>
       <c r="G25" s="23" t="n">
         <v>1</v>
@@ -11696,7 +10901,8 @@
       </c>
       <c r="B26" s="24" t="inlineStr">
         <is>
-          <t>Mobilização E Desmobilização Elevador Cremalheira</t>
+          <t>Filtro para piscina FM-25 p/ até 19 mil litros
+SODAMAR</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
@@ -11705,20 +10911,20 @@
         </is>
       </c>
       <c r="D26" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E26" s="26" t="n">
-        <v>1328</v>
+        <v>714</v>
       </c>
       <c r="F26" s="27" t="n">
-        <v>2656</v>
+        <v>714</v>
       </c>
       <c r="G26" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H26" s="24" t="inlineStr">
         <is>
-          <t>fg-scenarium</t>
+          <t>beco-castelo-chateau-de-versailes</t>
         </is>
       </c>
     </row>
@@ -11728,22 +10934,22 @@
       </c>
       <c r="B27" s="24" t="inlineStr">
         <is>
-          <t>13.28</t>
+          <t>BR - BOCAL DE RETORNO QUADRA AÇO INOX 316-L CRISTAL LED ENCAIXE P/ TUBO DE 50mm</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
         <is>
-          <t>2.6559999999999993</t>
+          <t>un</t>
         </is>
       </c>
       <c r="D27" s="25" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="E27" s="26" t="n">
-        <v>2655.999999999999</v>
+        <v>199</v>
       </c>
       <c r="F27" s="27" t="n">
-        <v>531.1999999999997</v>
+        <v>398</v>
       </c>
       <c r="G27" s="23" t="n">
         <v>1</v>
@@ -11760,7 +10966,8 @@
       </c>
       <c r="B28" s="24" t="inlineStr">
         <is>
-          <t>TAMPA GDA REBAIXADA C/ GRELHA 80X80cm CÓDIGO 3078</t>
+          <t>RALO DE FUNDO QUADRA ANTI-TURBILHÃO (16X16cm) E ANTI-APRISIONAMENTO COM DIFUSOR DE
+SOBREPOR EM AÇO INOX CRISTAL LED</t>
         </is>
       </c>
       <c r="C28" s="23" t="inlineStr">
@@ -11769,13 +10976,13 @@
         </is>
       </c>
       <c r="D28" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="26" t="n">
-        <v>1850</v>
+        <v>169</v>
       </c>
       <c r="F28" s="27" t="n">
-        <v>1850</v>
+        <v>338</v>
       </c>
       <c r="G28" s="23" t="n">
         <v>1</v>
@@ -11792,8 +10999,8 @@
       </c>
       <c r="B29" s="24" t="inlineStr">
         <is>
-          <t>Bomba BM-33 1/3 cv p/ piscinas de até 40 mil litros
-SODAMAR</t>
+          <t>RALO DE FUNDO QUADRA ANTI-TURBILHÃO (21X21cm) E ANTI-APRISIONAMENTO COM DIFUSOR DE
+SOBREPOR EM AÇO INOX CRISTAL LED.</t>
         </is>
       </c>
       <c r="C29" s="23" t="inlineStr">
@@ -11802,13 +11009,13 @@
         </is>
       </c>
       <c r="D29" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E29" s="26" t="n">
-        <v>1416</v>
+        <v>169</v>
       </c>
       <c r="F29" s="27" t="n">
-        <v>1416</v>
+        <v>338</v>
       </c>
       <c r="G29" s="23" t="n">
         <v>1</v>
@@ -11825,8 +11032,8 @@
       </c>
       <c r="B30" s="24" t="inlineStr">
         <is>
-          <t>Bomba 1/4cv BM-25 p/ piscinas de até 28 mil litro
-SODAMAR</t>
+          <t>BOCAL DE ASPIRAÇÃO QUADRA ANTI-TURBILHÃO E ANTI-APRISIONAMENTO AÇO INOX 316-L CRISTAL
+LED ENCAIXE P/ TUBO DE 50mm</t>
         </is>
       </c>
       <c r="C30" s="23" t="inlineStr">
@@ -11838,10 +11045,10 @@
         <v>1</v>
       </c>
       <c r="E30" s="26" t="n">
-        <v>1317</v>
+        <v>199</v>
       </c>
       <c r="F30" s="27" t="n">
-        <v>1317</v>
+        <v>199</v>
       </c>
       <c r="G30" s="23" t="n">
         <v>1</v>
@@ -11858,23 +11065,22 @@
       </c>
       <c r="B31" s="24" t="inlineStr">
         <is>
-          <t>Bomba 1/4 cv BM-25 p/ piscinas de até 28 mil litros
-SODAMAR</t>
+          <t>Piso Cerâmico / Piscina</t>
         </is>
       </c>
       <c r="C31" s="23" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="D31" s="25" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="E31" s="26" t="n">
-        <v>1055</v>
+        <v>85</v>
       </c>
       <c r="F31" s="27" t="n">
-        <v>1055</v>
+        <v>93.50000000000001</v>
       </c>
       <c r="G31" s="23" t="n">
         <v>1</v>
@@ -11891,8 +11097,7 @@
       </c>
       <c r="B32" s="24" t="inlineStr">
         <is>
-          <t>Filtro para piscina FM-36 p/ até 40 mil litros
-SODAMAR</t>
+          <t>BOCAL LADRÃO Grade 6,5x12cm EM LATÃO C/ ACABAMENTO INOX INAQUA</t>
         </is>
       </c>
       <c r="C32" s="23" t="inlineStr">
@@ -11904,10 +11109,10 @@
         <v>1</v>
       </c>
       <c r="E32" s="26" t="n">
-        <v>978</v>
+        <v>45.8</v>
       </c>
       <c r="F32" s="27" t="n">
-        <v>978</v>
+        <v>45.8</v>
       </c>
       <c r="G32" s="23" t="n">
         <v>1</v>
@@ -11924,23 +11129,22 @@
       </c>
       <c r="B33" s="24" t="inlineStr">
         <is>
-          <t>Filtro para piscina FM-30 p/ até 28 mil litros
-SODAMAR</t>
+          <t>Argamassa Colante AC III</t>
         </is>
       </c>
       <c r="C33" s="23" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D33" s="25" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E33" s="26" t="n">
-        <v>900</v>
+        <v>2.3</v>
       </c>
       <c r="F33" s="27" t="n">
-        <v>900</v>
+        <v>18.4</v>
       </c>
       <c r="G33" s="23" t="n">
         <v>1</v>
@@ -11957,29 +11161,29 @@
       </c>
       <c r="B34" s="24" t="inlineStr">
         <is>
-          <t>Tela  Elevador em Aço Galvanizado</t>
+          <t>Espaçador para Piso Cerâmico / Cruzeta 3,0mm c/ 100un</t>
         </is>
       </c>
       <c r="C34" s="23" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>un</t>
         </is>
       </c>
       <c r="D34" s="25" t="n">
-        <v>55.14</v>
+        <v>3</v>
       </c>
       <c r="E34" s="26" t="n">
-        <v>16.18</v>
+        <v>0.2</v>
       </c>
       <c r="F34" s="27" t="n">
-        <v>892.1652</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="G34" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H34" s="24" t="inlineStr">
         <is>
-          <t>fg-scenarium</t>
+          <t>beco-castelo-chateau-de-versailes</t>
         </is>
       </c>
     </row>
